--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_10.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_10.xlsx
@@ -575,46 +575,46 @@
         <v>39</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.775489602260095</v>
+        <v>-3.762976790210345</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.435204477415546</v>
+        <v>7.412391139742631</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.041988623992516</v>
+        <v>7.019838409533754</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.739918494405579</v>
+        <v>9.709663598717306</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.63669905464085</v>
+        <v>6.616268779793025</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.368944594329093</v>
+        <v>4.355444342654984</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.420848815828784</v>
+        <v>9.39132751653576</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.52377428975841</v>
+        <v>11.48731574581046</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.188791281792334</v>
+        <v>1.185445962069998</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.906792815380399</v>
+        <v>2.898006530217756</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.702380815141723</v>
+        <v>2.694029437192775</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.879514543236922</v>
+        <v>7.854732313002359</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.316481863852616</v>
+        <v>2.309552171391005</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.004705617142398921</v>
+        <v>-0.004296007168193228</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>28</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15.36370453693289</v>
+        <v>15.31468604242987</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.038538272935817</v>
+        <v>3.029528450656123</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.644258386481283</v>
+        <v>2.635926144409964</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.798946269247871</v>
+        <v>-0.7957078240167803</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.338144879579161</v>
+        <v>-1.333189511067744</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>13.26284942382442</v>
+        <v>13.22043471069787</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.604498946921971</v>
+        <v>9.573894427093144</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.561363172178993</v>
+        <v>5.543532077879867</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.079948210731082</v>
+        <v>9.051091929096977</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.230137618468547</v>
+        <v>8.204033178579451</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.027055522091771</v>
+        <v>8.00138892986709</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.64471915701576</v>
+        <v>11.60737909318458</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.643806522786043</v>
+        <v>7.619576703783558</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.7302591596828449</v>
+        <v>0.7283047254325368</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-11.03002368606364</v>
+        <v>-10.99387392015555</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.992991986629256</v>
+        <v>1.987233712102984</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.598460051593968</v>
+        <v>1.593391899181789</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.61079461876546</v>
+        <v>6.58994101616166</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.073441955892847</v>
+        <v>6.054328959290331</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.930876981173952</v>
+        <v>3.918141141588748</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.846954225583431</v>
+        <v>3.8345839422838</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.823312970404054</v>
+        <v>5.804319757056568</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.207425378819288</v>
+        <v>8.180913472564889</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.801940785739774</v>
+        <v>9.770262355495149</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1813338345978437</v>
+        <v>-0.1806935662594782</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1468323865170191</v>
+        <v>-0.1463901225343704</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5686652652261657</v>
+        <v>-0.566550066497193</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3184208089255094</v>
+        <v>-0.3169914418148423</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>69</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.926851534863154</v>
+        <v>6.904464845765474</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.931644698772409</v>
+        <v>-1.924549180770832</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.022876625267095</v>
+        <v>2.016258750350048</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.955189356892518</v>
+        <v>7.92929212472675</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.615187116472697</v>
+        <v>1.610322814586596</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.439783728845015</v>
+        <v>-2.431749760554887</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.073814311373241</v>
+        <v>-1.070212844719961</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.26549824273075</v>
+        <v>4.251138278870847</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.055824128109997</v>
+        <v>-3.045727377757601</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.908667728369096</v>
+        <v>-3.895766239388976</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.209066629974814</v>
+        <v>-1.205000097388144</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.174824767675702</v>
+        <v>-1.170960934815803</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.411867288910216</v>
+        <v>-7.386998442689432</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.346969128288059</v>
+        <v>-1.342088649308003</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.918326385671705</v>
+        <v>1.912046615196417</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3067686556119966</v>
+        <v>0.306562177860215</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.325898871532068</v>
+        <v>4.311273224530545</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.84477454137685</v>
+        <v>-5.825019746058054</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4969273415173845</v>
+        <v>-0.4948365347345884</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.616632278834217</v>
+        <v>-4.600965993617081</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.188815451178876</v>
+        <v>1.184908925625095</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.751869650947107</v>
+        <v>-0.7498073750425291</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.607409747258792</v>
+        <v>3.595378048602704</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.230235336005272</v>
+        <v>4.216127937173745</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.551650785267221</v>
+        <v>2.543170014781303</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3627328157781236</v>
+        <v>-0.3614722669979571</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.16531882811821</v>
+        <v>2.158750398226061</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.416624576767177</v>
+        <v>2.40897699433944</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>73</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.808506813360658</v>
+        <v>-1.802200348336726</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.430077608544821</v>
+        <v>3.41911904565174</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.075747821902262</v>
+        <v>-1.072337165440224</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4251415871220914</v>
+        <v>0.4240645529803757</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1137899591842881</v>
+        <v>-0.1129391582783157</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.55569307483583</v>
+        <v>1.550710700784457</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.09932051628354088</v>
+        <v>0.09901616433393201</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.003960169198216</v>
+        <v>1.000059225531146</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.315668602308939</v>
+        <v>2.307631655009523</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.210407478359144</v>
+        <v>4.195841920998681</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.234799020116846</v>
+        <v>-4.220250402183652</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.453780853778966</v>
+        <v>-1.448719997543506</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.62475131987572</v>
+        <v>-4.608206554925943</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.375189242876978</v>
+        <v>-4.359757896876658</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>87</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.276676622318497</v>
+        <v>7.251266307748338</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.816324979769171</v>
+        <v>6.792968100004913</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.723270953032937</v>
+        <v>8.692325829690276</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.40479305695608</v>
+        <v>5.38613536339637</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.867189601341352</v>
+        <v>4.850538612934031</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.468365488098875</v>
+        <v>7.442347924117044</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.385612784829547</v>
+        <v>7.359639284504915</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>12.67789326715401</v>
+        <v>12.63271787027406</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>13.77197767646944</v>
+        <v>13.72325331597008</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.466927092446994</v>
+        <v>9.433221436450793</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.5688184500784</v>
+        <v>11.52835102027457</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>12.75937715493681</v>
+        <v>12.71461100220259</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>15.79997129793707</v>
+        <v>15.74531502506475</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>17.20856501469962</v>
+        <v>17.14866597337948</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>118</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.883268828684358</v>
+        <v>-5.862268909237102</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9800005729266275</v>
+        <v>0.9765329088692312</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.129141406518592</v>
+        <v>3.116769292078281</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9806042868924649</v>
+        <v>-0.9771060380092464</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1768649079101223</v>
+        <v>0.1763193387503321</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.020870576395978</v>
+        <v>3.009537912591689</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.634750645437215</v>
+        <v>4.617293272768542</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.017684895131481</v>
+        <v>4.997781393180269</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.204736693087973</v>
+        <v>9.16983036249389</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.90379500470361</v>
+        <v>10.86292959987152</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>12.40090797415195</v>
+        <v>12.35509275841525</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>9.888892791241346</v>
+        <v>9.851999955635847</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>11.17013717177179</v>
+        <v>11.12918635712582</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>15.67711017535942</v>
+        <v>15.61934588766053</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>147</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.37050725802132</v>
+        <v>7.342854095917367</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.719203989086338</v>
+        <v>3.70507727180874</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.964075047374791</v>
+        <v>1.955165802016651</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.499120716811355</v>
+        <v>5.478309251923392</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.8752602192204293</v>
+        <v>0.8720231662923226</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.261303353526912</v>
+        <v>5.24059549800716</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.81530646655888</v>
+        <v>3.7996076496444</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.030679514601964</v>
+        <v>4.012981043853635</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.334801780040621</v>
+        <v>5.311876475493314</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.166251996494069</v>
+        <v>5.143991414196684</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.962349427808718</v>
+        <v>4.941208921419509</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.315941400121979</v>
+        <v>4.297336211627268</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.212531211310456</v>
+        <v>3.19860021329864</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.148162330695982</v>
+        <v>4.129665269650232</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>192</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.665572156191452</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.022252849070284</v>
+        <v>-2.014787609086881</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.417742026639608</v>
+        <v>-2.40997634532561</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.924957912973134</v>
+        <v>2.912309981269921</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.99397769675921</v>
+        <v>4.973850168359441</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.250797225621575</v>
+        <v>4.231980132587132</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.211086489172345</v>
+        <v>5.188133564304799</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.657533442158446</v>
+        <v>2.643498377084576</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.730541121080847</v>
+        <v>5.70362314584586</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.880081010019943</v>
+        <v>4.856637702970012</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.631282493584671</v>
+        <v>3.61327560032629</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.325272751158238</v>
+        <v>7.292624760047538</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.950842945259389</v>
+        <v>7.916410970163462</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9.251390538643733</v>
+        <v>9.210447582575398</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>248</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.299889933113114</v>
+        <v>-3.28702994864863</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3306007966941351</v>
+        <v>0.3289256309853954</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8711835638981356</v>
+        <v>-0.8690048796504186</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.548190778283356</v>
+        <v>-1.543233807731163</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3347527826953254</v>
+        <v>0.3319382142510463</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.193736140903987</v>
+        <v>-2.187277233660325</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.470801832310784</v>
+        <v>-1.468054971025843</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7262994258338864</v>
+        <v>-0.7276748328391989</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.190797953051622</v>
+        <v>-1.191558077982165</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3830348159061288</v>
+        <v>0.3757102050135117</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6316206813159653</v>
+        <v>-0.633727103117792</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.405768051480408</v>
+        <v>-1.405226081310396</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.638090550149151</v>
+        <v>-2.631509446437619</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.790956719087035</v>
+        <v>-2.78552015936009</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.710941241833737</v>
+        <v>3.723396718308535</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.376297620262484</v>
+        <v>-3.387051366081067</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.042026625361821</v>
+        <v>-3.050894273260489</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.374116392534539</v>
+        <v>-4.387385009588371</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.087243886829306</v>
+        <v>-3.096139650629183</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-5.349311620246823</v>
+        <v>-5.364879357135123</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.338230240177964</v>
+        <v>-4.349836869951226</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-7.168371887338182</v>
+        <v>-7.188309573284513</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.203925518883864</v>
+        <v>-5.216424467087741</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.22218613609364</v>
+        <v>-4.231281013594554</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.256050460612606</v>
+        <v>-6.272721031793608</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.491794224452853</v>
+        <v>-5.505590535781991</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-6.277418994026398</v>
+        <v>-6.294667305569554</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.031890172134865</v>
+        <v>-6.046905358601073</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.35707468384625</v>
+        <v>-1.364220374277771</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6963058041238455</v>
+        <v>-0.704023518730402</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.987123650800001</v>
+        <v>-3.011137720831201</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.788375859703059</v>
+        <v>-7.852943824523059</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.812967609248751</v>
+        <v>-6.868022825955748</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-8.415451711217955</v>
+        <v>-8.483511279585564</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.743564986746001</v>
+        <v>-7.803474830358475</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.832118936412591</v>
+        <v>-7.892558396460984</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.03109390524331</v>
+        <v>-9.09692028821695</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-10.0540979382238</v>
+        <v>-10.12695228128217</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-8.907460948310423</v>
+        <v>-8.975166311126898</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.385631553415166</v>
+        <v>-6.431012877808442</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.281858838757067</v>
+        <v>-5.321289119946705</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.800313081291442</v>
+        <v>-5.839839773746434</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>243</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1814587991314909</v>
+        <v>0.1793844637667945</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.627625291811718</v>
+        <v>0.6266097964503174</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.414980407555632</v>
+        <v>-1.408902324070723</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.774172868004861</v>
+        <v>0.7747929923847536</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.884342129952323</v>
+        <v>1.879807339157033</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.832502327638132</v>
+        <v>3.821470135016462</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.400674146594255</v>
+        <v>5.382393984411031</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.106972813049175</v>
+        <v>4.093322873897741</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3332845752100937</v>
+        <v>0.3316141666629875</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1063167296982641</v>
+        <v>-0.1066554667451527</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.337723639349704</v>
+        <v>1.333780691121355</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.277021805314817</v>
+        <v>-0.276913997502497</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.777416754543246</v>
+        <v>1.771157883143701</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.099532676484898</v>
+        <v>-2.093564763103707</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3291423249513556</v>
+        <v>0.3295016047575317</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7339107953283701</v>
+        <v>0.7341022825368952</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.549634098677949</v>
+        <v>1.550140852628857</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.891390096278002</v>
+        <v>2.892274826889796</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.970015825681436</v>
+        <v>3.971610452126718</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.865844477102542</v>
+        <v>3.867410040181596</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.357805981550065</v>
+        <v>1.358518926096622</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4843410338044478</v>
+        <v>0.4845962355456663</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.194380055685272</v>
+        <v>-1.194846575270212</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.451485373880004</v>
+        <v>-2.452514282487002</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.657915300284046</v>
+        <v>-2.65919535981083</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.217809461336586</v>
+        <v>-2.218715495031248</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.197657467096526</v>
+        <v>-1.198143617844416</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.567345211269135</v>
+        <v>-2.568398571270656</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>261</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.146408423084949</v>
+        <v>1.139399798400397</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.765801104137871</v>
+        <v>-2.753303727314972</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8614095651815461</v>
+        <v>-0.8565947247116199</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7323480613710487</v>
+        <v>-0.7263577005313664</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.503236931959286</v>
+        <v>-0.5009295955939805</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.510793452959732</v>
+        <v>-2.50034054626272</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.595852643888094</v>
+        <v>-2.58676216904172</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.681079630964788</v>
+        <v>-2.670606246913245</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.0511162616646601</v>
+        <v>-0.0511089489838028</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.289196346051249</v>
+        <v>-1.283573706979382</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.04187395998881982</v>
+        <v>0.04369725508663436</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.306426383783176</v>
+        <v>-0.3051377269092015</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4253685003932191</v>
+        <v>0.4235955815413277</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.830471596347536</v>
+        <v>1.822995475295706</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.220711047482659</v>
+        <v>-1.220473053290128</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.107006940676321</v>
+        <v>-2.105346861441021</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.688976383447127</v>
+        <v>-4.685948492747023</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.283416005806693</v>
+        <v>-1.282113024762999</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.093342291685417</v>
+        <v>-1.092619309586851</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.621275947053178</v>
+        <v>-2.619500349200919</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5154731901203959</v>
+        <v>-0.5152026314868507</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6207369180986717</v>
+        <v>-0.6202282779773611</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.045911684618169</v>
+        <v>-1.045328359699013</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6551919234113512</v>
+        <v>0.6549744402688304</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.8136111640824666</v>
+        <v>0.8134580033801484</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.6104592517807035</v>
+        <v>-0.610070410624644</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4287420258314967</v>
+        <v>0.4284498578910529</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.305674854309757</v>
+        <v>-1.305063366329705</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.590911244397702</v>
+        <v>-1.590261493020918</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.574820567379916</v>
+        <v>2.573836098211757</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3718193416477291</v>
+        <v>0.37266552772072</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.311529646411799</v>
+        <v>2.310817532625087</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.413246592490438</v>
+        <v>1.412462726394793</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9849962752915928</v>
+        <v>0.9850075466350745</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.01478809020127159</v>
+        <v>0.01480442574407448</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2721490266198288</v>
+        <v>0.272258708122088</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.386875429175376</v>
+        <v>2.385171865418002</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.898646694261295</v>
+        <v>1.897365520969828</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2431408078188397</v>
+        <v>0.2433368343334052</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.09076339059559</v>
+        <v>2.089314194577348</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.670455105724166</v>
+        <v>1.669059583632482</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.008066419332586</v>
+        <v>3.005737437647902</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>233</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.729737645455266</v>
+        <v>3.706392741598414</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.697363922691849</v>
+        <v>4.676900952374226</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.16424685106071</v>
+        <v>5.145559025269357</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.717082268720191</v>
+        <v>2.70847441621045</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.631094245232958</v>
+        <v>5.600942359931707</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.93143224015148</v>
+        <v>5.904414674707617</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.262231169885844</v>
+        <v>3.24457366129807</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.6324595572381071</v>
+        <v>0.631467515735352</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.438912798340077</v>
+        <v>1.428836728265573</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.740737323532159</v>
+        <v>2.724634290018656</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.53066474739164</v>
+        <v>2.519880965701134</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.01941944825636455</v>
+        <v>-0.02084317309074635</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8717081336269672</v>
+        <v>-0.870282333391927</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.208871996081761</v>
+        <v>-3.195668297252993</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>215</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-8.307391808582068</v>
+        <v>-8.259392192578972</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-7.138525809580401</v>
+        <v>-7.087235497316868</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.681512793797133</v>
+        <v>-5.634409152917321</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.756796630884885</v>
+        <v>-2.731669796775286</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.291723011042457</v>
+        <v>-3.277246429103556</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.002404356628958</v>
+        <v>-2.982699807775667</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.678520716676189</v>
+        <v>-1.672084687838627</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2837457812042103</v>
+        <v>-0.278802970341026</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.146844413038941</v>
+        <v>-3.130500530941958</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.660161278493597</v>
+        <v>-1.655044320621023</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.0002302511890803771</v>
+        <v>0.0006674713404208887</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5062768741074706</v>
+        <v>0.5001669077556343</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.663386563319285</v>
+        <v>-3.641017935747406</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.009031023501549</v>
+        <v>-1.995947766261786</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>146</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-9.342753388703123</v>
+        <v>-9.253910452776765</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.057975675462522</v>
+        <v>-2.019184361281489</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.659964894984817</v>
+        <v>1.671309962205193</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.648822498327085</v>
+        <v>-1.617287467392138</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.629117602128304</v>
+        <v>-5.583945885823866</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.040654552361545</v>
+        <v>-5.980469798218422</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-10.26334753369172</v>
+        <v>-10.17479255658663</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.980272573101011</v>
+        <v>-7.902249927970949</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.652248215124047</v>
+        <v>-6.593386800454581</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.049001212121397</v>
+        <v>-4.018854451235896</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.263017912754357</v>
+        <v>-4.223607775553432</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.222018058040781</v>
+        <v>-4.189224618208044</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.890690970139772</v>
+        <v>-1.869753201755643</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.638322958916206</v>
+        <v>-1.620031869479355</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7.360576278330178</v>
+        <v>7.350298222251496</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6329518227284652</v>
+        <v>0.6394171173366345</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.318350804879607</v>
+        <v>4.315787889380246</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.916609300379811</v>
+        <v>5.909066211129094</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.180052714621695</v>
+        <v>3.17407375698879</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.743272497434944</v>
+        <v>2.742334391950735</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.921927459609719</v>
+        <v>1.92230655703144</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.451685579934662</v>
+        <v>1.455123158249982</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.130792421040788</v>
+        <v>2.129417389714696</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1921184792510573</v>
+        <v>-0.1912960306073472</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3371179619326057</v>
+        <v>0.3392447627220889</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.110733994882658</v>
+        <v>1.108922037714621</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.78623866390366</v>
+        <v>-0.7819208085244611</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.412549505635994</v>
+        <v>2.408976994340087</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.223542811865492</v>
+        <v>2.231245208821385</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.87945515074918</v>
+        <v>5.900025402371519</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.418845661110879</v>
+        <v>6.463414539626001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.348635911045136</v>
+        <v>2.356837775127204</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.101346367457154</v>
+        <v>-0.1005621694625844</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.818762570216954</v>
+        <v>7.889393215480148</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.986217778829506</v>
+        <v>2.996967190515555</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.338548379849506</v>
+        <v>6.375937637887901</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.454996616650128</v>
+        <v>2.468783905551753</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.24685309006253</v>
+        <v>-1.265956664091561</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.433379151086427</v>
+        <v>-1.470709988409141</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.265909901503818</v>
+        <v>-4.320942215679118</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.712299279900712</v>
+        <v>-3.779658365085503</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.480805210918184</v>
+        <v>-3.529937032809272</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.197663672322648</v>
+        <v>-3.243694694336178</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.992335876836208</v>
+        <v>-2.049165428864775</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.795655287658192</v>
+        <v>-3.850334284980335</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8485007465999459</v>
+        <v>-0.8717450400222546</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.024624397787164</v>
+        <v>-2.043032514127674</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3187874069717083</v>
+        <v>-0.3248924988055464</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.441504050622633</v>
+        <v>2.447516641065029</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.8448041334274805</v>
+        <v>-0.8768096148593258</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.333172930092744</v>
+        <v>-2.366380929613051</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3479855863532819</v>
+        <v>-0.3593632574981243</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.776569765524123</v>
+        <v>-4.849830867529995</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5086431072261206</v>
+        <v>-0.529733424470237</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.337021269779015</v>
+        <v>3.335726250299153</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.152898594172882</v>
+        <v>2.156876154004003</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.997127717525906</v>
+        <v>6.058979725878984</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.159139010221992</v>
+        <v>8.212417472862775</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>9.651062756455644</v>
+        <v>9.77308268382545</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>17.32848570038384</v>
+        <v>17.61998625460233</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.356102221160711</v>
+        <v>7.490523170007258</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>10.57967143741816</v>
+        <v>10.77400860009556</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.632129917139821</v>
+        <v>8.766197959746378</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.97850584039217</v>
+        <v>12.1451684071187</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13.78031375721593</v>
+        <v>14.00724544401331</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.269811213697444</v>
+        <v>7.38788948975462</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.79738919734278</v>
+        <v>12.95236693466781</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>14.67059550787016</v>
+        <v>14.90982701509017</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>16.16911288285426</v>
+        <v>16.41264932722213</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.71848244026648</v>
+        <v>10.8931398902677</v>
       </c>
     </row>
     <row r="31">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.01272</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4084~4097</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4084</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.1304328050036005</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.01182</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4045~4058</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4045</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.1679712411502976</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.01093</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4017~4030</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4017</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.06239294529871131</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.01003</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3976~3989</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3976</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.176403745470644</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.009136</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3907~3920</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3907</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.05758208795328557</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.00824</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3839~3852</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3839</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.02473405777548976</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.007345</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3766~3779</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3766</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.06014728444733919</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.006449</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3679~3692</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3679</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1099063592132197</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.005553</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3561~3574</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3561</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.08070829422762671</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.004657</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3414~3427</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3414</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.2319851541755398</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.003762</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3222~3235</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3222</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.3450611950167755</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.002866</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2974~2987</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2974</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.099732260618417</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.00197</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2702~2713</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2702</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.4845920245962674</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.001074</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2441~2449</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2441</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3905391777028342</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.0001786</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2198~2206</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2198</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.4535471144076197</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.0007171</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1951~1958</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1951</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.5526824468698379</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.001613</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1690~1697</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1690</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.8140040243938245</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.002509</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1416~1422</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1416</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.7353511190847968</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.003404</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1140~1145</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1140</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.5283728180265683</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.0043</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>907~912</t>
-        </is>
+      <c r="B25" t="n">
+        <v>907</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.616245337753831</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.005196</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>692~697</t>
-        </is>
+      <c r="B26" t="n">
+        <v>692</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.4477381503782638</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.006092</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>546~551</t>
-        </is>
+      <c r="B27" t="n">
+        <v>546</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.041951879427046</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.006987</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>410~414</t>
-        </is>
+      <c r="B28" t="n">
+        <v>410</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.612841873026738</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.007883</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>306~308</t>
-        </is>
+      <c r="B29" t="n">
+        <v>306</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.40266557589392</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.008779</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>236~237</t>
-        </is>
+      <c r="B30" t="n">
+        <v>236</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.780823283165553</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.009675</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>184~184</t>
-        </is>
+      <c r="B31" t="n">
+        <v>184</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.854387766746541</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.01057</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>145~145</t>
-        </is>
+      <c r="B32" t="n">
+        <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>4.747940990134857</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.01147</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>115~115</t>
-        </is>
+      <c r="B33" t="n">
+        <v>115</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>6.63699646239872</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.01236</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>92~92</t>
-        </is>
+      <c r="B34" t="n">
+        <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>6.202213853703071</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.01326</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>8.220847394075733</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.01272</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.01182</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>123~123</t>
-        </is>
+      <c r="B7" t="n">
+        <v>123</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-5.338966775494526</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.01093</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>151~151</t>
-        </is>
+      <c r="B8" t="n">
+        <v>151</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-1.500060836766259</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.01003</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>192~192</t>
-        </is>
+      <c r="B9" t="n">
+        <v>192</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-3.535104986876647</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.009136</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>261~261</t>
-        </is>
+      <c r="B10" t="n">
+        <v>261</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.7693003891754913</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.00824</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>329~329</t>
-        </is>
+      <c r="B11" t="n">
+        <v>329</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2138030618513156</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.007345</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>402~402</t>
-        </is>
+      <c r="B12" t="n">
+        <v>402</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.5033885689661943</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.006449</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>489~489</t>
-        </is>
+      <c r="B13" t="n">
+        <v>489</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.8807948086243869</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.005553</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>607~607</t>
-        </is>
+      <c r="B14" t="n">
+        <v>607</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.4341302477223365</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.004657</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>754~754</t>
-        </is>
+      <c r="B15" t="n">
+        <v>754</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.087463536553955</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.003762</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>946~946</t>
-        </is>
+      <c r="B16" t="n">
+        <v>946</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.206350263299534</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.002866</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1194~1194</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1194</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.2703807752674052</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.00197</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1466~1468</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1466</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.9125562301987458</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.001074</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1727~1732</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1727</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.566607869166468</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.0001786</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1970~1975</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1970</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5192199076381243</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.0007171</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2217~2223</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2217</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.4980146712430198</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.001613</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2478~2484</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2478</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.5661430002409134</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.002509</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2752~2759</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2752</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.3880404764554868</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.003404</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3028~3036</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3028</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.2074839459296882</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.0043</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3261~3269</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3261</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.4585347602427632</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.005196</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3476~3484</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3476</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.0824165062030886</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.006092</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3622~3630</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3622</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.4548708270970252</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.006987</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3758~3767</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3758</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.1706350284658811</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.007883</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3862~3873</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3862</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1051088598433267</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.008779</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3932~3944</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3932</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.1607811193986137</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.009675</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3984~3997</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3984</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.07912758716018686</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.01057</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4023~4036</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4023</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.164399668079156</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.01147</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4053~4066</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4053</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1815839178489256</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.01236</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4076~4089</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4076</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.1334481025528476</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.01326</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4084~4097</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4084</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.162464436880704</v>

--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_10.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_10.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-10 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-10 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>39</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.762976790210345</v>
+        <v>-3.750498711038361</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.412391139742631</v>
+        <v>7.425266860328556</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.019838409533754</v>
+        <v>7.032813999794037</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.709663598717306</v>
+        <v>9.722615566569623</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.616268779793025</v>
+        <v>6.629353164311169</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.355444342654984</v>
+        <v>4.368462884183067</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.39132751653576</v>
+        <v>9.404374520754729</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.48731574581046</v>
+        <v>11.50048088983115</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.185445962069998</v>
+        <v>1.198628309897863</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.898006530217756</v>
+        <v>2.91139874176087</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.694029437192775</v>
+        <v>2.707476989481314</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.854732313002359</v>
+        <v>7.868178726963855</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.309552171391005</v>
+        <v>2.323104913472562</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.004296007168193228</v>
+        <v>-0.01472564286518008</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>28</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15.31468604242987</v>
+        <v>15.32717865130133</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.029528450656123</v>
+        <v>3.042400442787965</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.635926144409964</v>
+        <v>2.648898308166444</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.7957078240167803</v>
+        <v>-0.7827627044248757</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.333189511067744</v>
+        <v>-1.320109930328037</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>13.22043471069787</v>
+        <v>13.23345726657199</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.573894427093144</v>
+        <v>9.586941255785376</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.543532077879867</v>
+        <v>5.556694821242438</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.051091929096977</v>
+        <v>9.064276442898475</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.204033178579451</v>
+        <v>8.217426499839576</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.00138892986709</v>
+        <v>8.014837313577658</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.60737909318458</v>
+        <v>11.62082588982511</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.619576703783558</v>
+        <v>7.633129721899465</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897327646</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.99387392015555</v>
+        <v>-10.98140316999077</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.987233712102984</v>
+        <v>2.000104297658126</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.593391899181789</v>
+        <v>1.606362765372161</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.58994101616166</v>
+        <v>6.602890195137377</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.054328959290331</v>
+        <v>6.067412179842258</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.918141141588748</v>
+        <v>3.93115876210144</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.8345839422838</v>
+        <v>3.847627970074363</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.804319757056568</v>
+        <v>5.817482318645965</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.180913472564889</v>
+        <v>8.194097513430876</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.770262355495149</v>
+        <v>9.78365590294014</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1806935662594782</v>
+        <v>-0.1672468623495362</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1463901225343704</v>
+        <v>-0.1329448819689674</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.566550066497193</v>
+        <v>-0.5529976103415422</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3169914418148423</v>
+        <v>-0.3274210775118931</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>69</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.904464845765474</v>
+        <v>6.916949078997568</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.924549180770832</v>
+        <v>-1.911682722685491</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.016258750350048</v>
+        <v>2.029228933233647</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.92929212472675</v>
+        <v>7.942241452691377</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.610322814586596</v>
+        <v>1.623402742132456</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.431749760554887</v>
+        <v>-2.418736113933718</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.070212844719961</v>
+        <v>-1.057171638154017</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.251138278870847</v>
+        <v>4.264299775651253</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.045727377757601</v>
+        <v>-3.032547348401252</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.895766239388976</v>
+        <v>-3.882376523928563</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.205000097388144</v>
+        <v>-1.19155389349217</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.170960934815803</v>
+        <v>-1.157516027162551</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.386998442689432</v>
+        <v>-7.373446535321015</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.342088649308003</v>
+        <v>-1.352518285008131</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.912046615196417</v>
+        <v>1.924525314910575</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.306562177860215</v>
+        <v>0.3194288439286979</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.311273224530545</v>
+        <v>4.324243852458771</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.825019746058054</v>
+        <v>-5.8120806003068</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4948365347345884</v>
+        <v>-0.4817589572004266</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.600965993617081</v>
+        <v>-4.58795460895346</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.184908925625095</v>
+        <v>1.197950291074747</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7498073750425291</v>
+        <v>-0.7366485440738586</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.595378048602704</v>
+        <v>3.608559624831372</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.216127937173745</v>
+        <v>4.229519265264756</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.543170014781303</v>
+        <v>2.556616576790425</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3614722669979571</v>
+        <v>-0.3480275182992187</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.158750398226061</v>
+        <v>2.172302787556312</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.40897699433944</v>
+        <v>2.398547358643285</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>73</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.802200348336726</v>
+        <v>-1.78972660429104</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.41911904565174</v>
+        <v>3.431986728328674</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.072337165440224</v>
+        <v>-1.059371939440148</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4240645529803757</v>
+        <v>0.4370064482567528</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1129391582783157</v>
+        <v>-0.09986259412446685</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.550710700784457</v>
+        <v>1.56372427451489</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.09901616433393201</v>
+        <v>0.112056085968895</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.000059225531146</v>
+        <v>1.013217957139268</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.307631655009523</v>
+        <v>2.32081218235512</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.195841920998681</v>
+        <v>4.209232770499796</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.220250402183652</v>
+        <v>-4.206805651222048</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.448719997543506</v>
+        <v>-1.435275686045024</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.608206554925943</v>
+        <v>-4.594654774295115</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.359757896876658</v>
+        <v>-4.370187532575436</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>87</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.251266307748338</v>
+        <v>7.263746536896697</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.792968100004913</v>
+        <v>6.805837056869727</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.692325829690276</v>
+        <v>8.7052971151344</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.38613536339637</v>
+        <v>5.399079308550327</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.850538612934031</v>
+        <v>4.863616976542708</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.442347924117044</v>
+        <v>7.455363735678262</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.359639284504915</v>
+        <v>7.372681812220975</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>12.63271787027406</v>
+        <v>12.64588080299908</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>13.72325331597008</v>
+        <v>13.73643729925797</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.433221436450793</v>
+        <v>9.446613264441325</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.52835102027457</v>
+        <v>11.54179867353696</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>12.71461100220259</v>
+        <v>12.72805704899209</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>15.74531502506475</v>
+        <v>15.75886810819061</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>17.14866597337948</v>
+        <v>17.13823633768184</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>118</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.862268909237102</v>
+        <v>-5.849804073836097</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9765329088692312</v>
+        <v>0.9893943855760838</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.116769292078281</v>
+        <v>3.129734122430229</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9771060380092464</v>
+        <v>-0.9641688841403493</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1763193387503321</v>
+        <v>0.1893927176874755</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.009537912591689</v>
+        <v>3.022549637533274</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.617293272768542</v>
+        <v>4.630333152808475</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.997781393180269</v>
+        <v>5.010940018269189</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.16983036249389</v>
+        <v>9.183012007811939</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.86292959987152</v>
+        <v>10.87632128107816</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>12.35509275841525</v>
+        <v>12.36854020349138</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>9.851999955635847</v>
+        <v>9.865445303525753</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>11.12918635712582</v>
+        <v>11.14273897386829</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>15.61934588766053</v>
+        <v>15.60891625196199</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>147</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.342854095917367</v>
+        <v>7.35532868268978</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.70507727180874</v>
+        <v>3.717937882135885</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.955165802016651</v>
+        <v>1.968126505134194</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.478309251923392</v>
+        <v>5.491248616834511</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.8720231662923226</v>
+        <v>0.8850941928905129</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.24059549800716</v>
+        <v>5.253606495207009</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.7996076496444</v>
+        <v>3.812645210544773</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.012981043853635</v>
+        <v>4.026137637511177</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.311876475493314</v>
+        <v>5.325055448910319</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.143991414196684</v>
+        <v>5.157380378858612</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.941208921419509</v>
+        <v>4.954653936988528</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.297336211627268</v>
+        <v>4.310780197854228</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.19860021329864</v>
+        <v>3.212151955540804</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.129665269650232</v>
+        <v>4.11923563395208</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>192</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.665572156191452</v>
+        <v>1.678035566122972</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.014787609086881</v>
+        <v>-2.001938315478064</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.40997634532561</v>
+        <v>-2.397024871875843</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.912309981269921</v>
+        <v>2.925243232909224</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.973850168359441</v>
+        <v>4.986920640731874</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.231980132587132</v>
+        <v>4.244987422780319</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.188133564304799</v>
+        <v>5.201169323036893</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.643498377084576</v>
+        <v>2.656651883811058</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.70362314584586</v>
+        <v>5.716800519240159</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.856637702970012</v>
+        <v>4.870025082462924</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.61327560032629</v>
+        <v>3.62671910150258</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.292624760047538</v>
+        <v>7.306068543448063</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.916410970163462</v>
+        <v>7.929962748976436</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9.210447582575398</v>
+        <v>9.200017946877246</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>248</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.28702994864863</v>
+        <v>-3.274582075284052</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3289256309853954</v>
+        <v>0.3417688349634034</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8690048796504186</v>
+        <v>-0.8560600244349459</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.543233807731163</v>
+        <v>-1.530311857320534</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3319382142510463</v>
+        <v>0.3449987228244211</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.187277233660325</v>
+        <v>-2.174280409824995</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.468054971025843</v>
+        <v>-1.455028352601019</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7276748328391989</v>
+        <v>-0.7145273455857151</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.191558077982165</v>
+        <v>-1.178387235312222</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3757102050135117</v>
+        <v>0.3890932982393736</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.633727103117792</v>
+        <v>-0.6202868719393848</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.405226081310396</v>
+        <v>-1.391785270193566</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.631509446437619</v>
+        <v>-2.617959358676217</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.78552015936009</v>
+        <v>-2.795949795058242</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>272</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.723396718308535</v>
+        <v>3.73598208267515</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.387051366081067</v>
+        <v>-3.374080233434285</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.050894273260489</v>
+        <v>-3.037817737765863</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.387385009588371</v>
+        <v>-4.374330992832107</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.096139650629183</v>
+        <v>-3.082944617800287</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-5.364879357135123</v>
+        <v>-5.351747618177107</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.349836869951226</v>
+        <v>-4.33667374888207</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-7.188309573284513</v>
+        <v>-7.37586802577438</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.216424467087741</v>
+        <v>-5.40226776157089</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.231281013594554</v>
+        <v>-4.217904512275503</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.272721031793608</v>
+        <v>-6.25928635858947</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.505590535781991</v>
+        <v>-5.492153059030478</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-6.294667305569554</v>
+        <v>-6.281118901097052</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.046905358601073</v>
+        <v>-6.057334994299225</v>
       </c>
     </row>
     <row r="18">
@@ -1199,150 +1199,150 @@
         <v>261</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.364220374277771</v>
+        <v>-1.351542287796725</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.704023518730402</v>
+        <v>-0.6909424711625363</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.011137720831201</v>
+        <v>-2.997952574638852</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.852943824523059</v>
+        <v>-7.839781934722382</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.868022825955748</v>
+        <v>-6.854717517912178</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-8.483511279585564</v>
+        <v>-8.470266300785269</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.803474830358475</v>
+        <v>-7.790197297766312</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.892558396460984</v>
+        <v>-7.882425337013572</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.09692028821695</v>
+        <v>-9.087041160552431</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-10.12695228128217</v>
+        <v>-10.32731259545643</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-8.975166311126898</v>
+        <v>-9.178058348292211</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.431012877808442</v>
+        <v>-6.631950491740369</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.321289119946705</v>
+        <v>-5.307742394638225</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.839839773746434</v>
+        <v>-5.850269409444586</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0006263</t>
+          <t>X ≈ -0.0006264</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>243</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1793844637667945</v>
+        <v>0.1918306059209414</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6266097964503174</v>
+        <v>0.63944945468144</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.408902324070723</v>
+        <v>-1.395958129856112</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7747929923847536</v>
+        <v>0.7877206768327127</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.879807339157033</v>
+        <v>1.892877943084194</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.821470135016462</v>
+        <v>3.834484039670102</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.382393984411031</v>
+        <v>5.395441845542969</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.093322873897741</v>
+        <v>4.108210125586929</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3316141666629875</v>
+        <v>0.3450217066860262</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1066554667451527</v>
+        <v>-0.09320799696136817</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.333780691121355</v>
+        <v>1.347730853360105</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.276913997502497</v>
+        <v>-0.2634751847589314</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.771157883143701</v>
+        <v>1.784703732549772</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.093564763103707</v>
+        <v>-2.103994398801767</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002693</t>
+          <t>X ≈ 0.0002692</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>247</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3295016047575317</v>
+        <v>0.3420361955311293</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7341022825368952</v>
+        <v>0.7470367224397094</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.550140852628857</v>
+        <v>1.563186392391124</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.892274826889796</v>
+        <v>2.905306084811031</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.971610452126718</v>
+        <v>3.984787060899713</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.867410040181596</v>
+        <v>3.880530270790935</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.358518926096622</v>
+        <v>1.371673107060737</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4845962355456663</v>
+        <v>0.4980623350741453</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.194846575270212</v>
+        <v>-1.182168993329242</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.452514282487002</v>
+        <v>-2.440258566251018</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.65919535981083</v>
+        <v>-2.647168042509087</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.218715495031248</v>
+        <v>-2.206275352060146</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.198143617844416</v>
+        <v>-1.413875598086058</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.568398571270656</v>
+        <v>-2.578828206968907</v>
       </c>
     </row>
     <row r="21">
@@ -1355,98 +1355,98 @@
         <v>261</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.139399798400397</v>
+        <v>1.151816912123586</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.753303727314972</v>
+        <v>-2.740498406571717</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8565947247116199</v>
+        <v>-0.8436721829289269</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7263577005313664</v>
+        <v>-0.7134470422368722</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5009295955939805</v>
+        <v>-0.4878691648098297</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.50034054626272</v>
+        <v>-2.487332444181391</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.58676216904172</v>
+        <v>-2.573713115508092</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.670606246913245</v>
+        <v>-2.658921435339586</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.0511089489838028</v>
+        <v>-0.03791125469778933</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.283573706979382</v>
+        <v>-1.270971813479669</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.04369725508663436</v>
+        <v>0.05689407806865887</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3051377269092015</v>
+        <v>-0.2918695320282225</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4235955815413277</v>
+        <v>0.4374049020146131</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.822995475295706</v>
+        <v>1.812565839597553</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.002061</t>
+          <t>X ≈ 0.00206</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.220473053290128</v>
+        <v>-1.2063378085127</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.105346861441021</v>
+        <v>-2.080276837476475</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.685948492747023</v>
+        <v>-4.650624665644671</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.282113024762999</v>
+        <v>-1.259572155835265</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.092619309586851</v>
+        <v>-1.07422010021785</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.619500349200919</v>
+        <v>-2.59334507300936</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5152026314868507</v>
+        <v>-0.5001539408349203</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6202282779773611</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.045328359699013</v>
+        <v>-1.028506865982962</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6549744402688304</v>
+        <v>0.6670288831417182</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.8134580033801484</v>
+        <v>0.8259640885178925</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.610070410624644</v>
+        <v>-0.5942032136722375</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4284498578910529</v>
+        <v>0.4401913875598069</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.305063366329705</v>
+        <v>-1.152254780395481</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>276</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.590261493020918</v>
+        <v>-1.577052545764914</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.573836098211757</v>
+        <v>2.585585049435004</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.37266552772072</v>
+        <v>0.3866503762008264</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.310817532625087</v>
+        <v>2.32301575866493</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.412462726394793</v>
+        <v>1.424743090559431</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9850075466350745</v>
+        <v>0.9981710372865393</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.01480442574407448</v>
+        <v>-0.1702924120156268</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.272258708122088</v>
+        <v>0.2854397174173258</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.385171865418002</v>
+        <v>2.398370604372765</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.897365520969828</v>
+        <v>1.910770648622659</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2433368343334052</v>
+        <v>0.256794128043623</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.669059583632482</v>
+        <v>1.682615629984085</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.005737437647902</v>
+        <v>2.99530780194975</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>233</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.706392741598414</v>
+        <v>3.713978739964773</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.676900952374226</v>
+        <v>4.685476921095471</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.145559025269357</v>
+        <v>5.154629088586702</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.70847441621045</v>
+        <v>2.719577539483076</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.600942359931707</v>
+        <v>5.607930014355567</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.904414674707617</v>
+        <v>5.912006328868614</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.24457366129807</v>
+        <v>3.257639915598546</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.631467515735352</v>
+        <v>0.6446485250305898</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.428836728265573</v>
+        <v>1.442035467220336</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.724634290018656</v>
+        <v>2.738039417671487</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.519880965701134</v>
+        <v>2.533338259411352</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.02084317309074635</v>
+        <v>-0.007390884370636286</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.870282333391927</v>
+        <v>-0.8567262870403241</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.195668297252993</v>
+        <v>-3.206097932951145</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>215</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-8.259392192578972</v>
+        <v>-8.237831514516948</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-7.087235497316868</v>
+        <v>-7.06456688046547</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.634409152917321</v>
+        <v>-5.612384834328047</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.731669796775286</v>
+        <v>-2.713948417898884</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.277246429103556</v>
+        <v>-3.261418691666741</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.982699807775667</v>
+        <v>-2.965808069910878</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.672084687838627</v>
+        <v>-1.659018433538151</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.278802970341026</v>
+        <v>-0.2656219610457882</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.130500530941958</v>
+        <v>-3.117301791987195</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.655044320621023</v>
+        <v>-1.641639192968192</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.0006674713404208887</v>
+        <v>0.01412476505063864</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5001669077556343</v>
+        <v>0.5136191964757444</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.641017935747406</v>
+        <v>-3.627461889395803</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.995947766261786</v>
+        <v>-2.006377401959938</v>
       </c>
     </row>
     <row r="26">
@@ -1615,98 +1615,98 @@
         <v>146</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-9.253910452776765</v>
+        <v>-9.224637136186324</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.019184361281489</v>
+        <v>-1.999319958059218</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.671309962205193</v>
+        <v>1.685969708892408</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.617287467392138</v>
+        <v>-1.598477627606599</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.583945885823866</v>
+        <v>-5.562119038365239</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.980469798218422</v>
+        <v>-5.955557581747982</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-10.17479255658663</v>
+        <v>-10.16172630228616</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.902249927970949</v>
+        <v>-7.889068918675711</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.593386800454581</v>
+        <v>-6.580188061499818</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.018854451235896</v>
+        <v>-4.005449323583065</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.223607775553432</v>
+        <v>-4.210150481843215</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.189224618208044</v>
+        <v>-4.175772329487934</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.869753201755643</v>
+        <v>-1.85619715540404</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.620031869479355</v>
+        <v>-1.630461505177507</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.00654</t>
+          <t>X ≈ 0.006539</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>136</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7.350298222251496</v>
+        <v>7.351957663731177</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6394171173366345</v>
+        <v>0.6586249380516165</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.315787889380246</v>
+        <v>3.907314058815459</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.909066211129094</v>
+        <v>5.913633685259946</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.17407375698879</v>
+        <v>3.180609110531996</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.742334391950735</v>
+        <v>2.754167153675567</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.92230655703144</v>
+        <v>1.935372811331916</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.455123158249982</v>
+        <v>1.46830416754522</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.129417389714696</v>
+        <v>2.142616128669459</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1912960306073472</v>
+        <v>-0.1778909029545162</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3392447627220889</v>
+        <v>0.3527020564323067</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.108922037714621</v>
+        <v>1.122374326434731</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.7819208085244611</v>
+        <v>-0.7683647621728582</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.408976994340087</v>
+        <v>2.398547358641935</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>104</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.231245208821385</v>
+        <v>2.242983300921452</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.900025402371519</v>
+        <v>5.357264934464517</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.463414539626001</v>
+        <v>6.476421671043603</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.356837775127204</v>
+        <v>1.834617995992993</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1005621694625844</v>
+        <v>-0.08851860901405217</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.889393215480148</v>
+        <v>7.883514279744887</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.996967190515555</v>
+        <v>3.010033444816031</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.375937637887901</v>
+        <v>6.389118647183139</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.468783905551753</v>
+        <v>2.481982644506516</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.265956664091561</v>
+        <v>-1.25255153643873</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.470709988409141</v>
+        <v>-1.457252694698923</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.320942215679118</v>
+        <v>-4.307489926959008</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.779658365085503</v>
+        <v>-3.7661023187339</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.529937032809272</v>
+        <v>-3.540366668507424</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>70</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.243694694336178</v>
+        <v>-3.210644815252166</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.049165428864775</v>
+        <v>-2.036255619288724</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.850334284980335</v>
+        <v>-3.837327153562732</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8717450400222546</v>
+        <v>-0.8587658976237904</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.043032514127674</v>
+        <v>-2.806604310539647</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.3100039790929117</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.8768096148593258</v>
+        <v>-0.863628605564088</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.366380929613051</v>
+        <v>-2.353182190658288</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3593632574981243</v>
+        <v>-0.3459581298452932</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.849830867529995</v>
+        <v>-4.836373573819778</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.529733424470237</v>
+        <v>-0.5162811357501269</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.335726250299153</v>
+        <v>3.349282296650756</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.156876154004003</v>
+        <v>2.146446518305851</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>52</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.058979725878984</v>
+        <v>5.017467938437903</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.212417472862775</v>
+        <v>8.225327282438826</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>9.77308268382545</v>
+        <v>9.786089815243052</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>17.61998625460233</v>
+        <v>17.6329653970008</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.490523170007258</v>
+        <v>7.503633974382197</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>10.77400860009556</v>
+        <v>9.732199175714783</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.766197959746378</v>
+        <v>8.779264214046854</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>12.1451684071187</v>
+        <v>12.15834941641393</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>14.00724544401331</v>
+        <v>14.02044418296808</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.38788948975462</v>
+        <v>7.401294617407451</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.95236693466781</v>
+        <v>12.96582422837803</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>14.90982701509017</v>
+        <v>14.92327930381028</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>16.41264932722213</v>
+        <v>16.42620537357374</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.8931398902677</v>
+        <v>10.88271025456955</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>39</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-8.903694730466427</v>
+        <v>-8.891172440790804</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.869347041184774</v>
+        <v>4.882256850760825</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>17.29499115510097</v>
+        <v>17.30799828651858</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.040628903093086</v>
+        <v>2.053608045491551</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.194515380328653</v>
+        <v>9.207626184703592</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.927854753941709</v>
+        <v>6.940897650236074</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.279018472566868</v>
+        <v>4.292084726867344</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.375937637887965</v>
+        <v>6.389118647183203</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.87904031580819</v>
+        <v>8.892239054762953</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.464812566677736</v>
+        <v>5.478217694330567</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.273516536070339</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.730339835603019</v>
+        <v>2.743792124323129</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.310085224658089</v>
+        <v>2.323641271009691</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>30</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.56165473349238</v>
+        <v>12.57456454306843</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.963705826170006</v>
+        <v>8.97668496856847</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.425284611097837</v>
+        <v>8.438395415472776</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.277273451186495</v>
+        <v>-1.26423055489213</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.304659498207819</v>
+        <v>5.317725752508295</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.170809432759675</v>
+        <v>8.183990442054913</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.92635102821612</v>
+        <v>13.93975615586895</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.72159770389858</v>
+        <v>13.7350549976088</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.75598086124397</v>
+        <v>13.76943314996408</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.00239291696575</v>
+        <v>10.01594896331736</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.918780915908727</v>
+        <v>6.908351280210574</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>23</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.376126897181337</v>
+        <v>8.388649186856959</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.416727197260549</v>
+        <v>2.4296370068366</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.325967596292564</v>
+        <v>-2.312960464874962</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-10.8913666375981</v>
+        <v>-10.87838749519964</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-7.08196176571375</v>
+        <v>-7.068850961338811</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.258958432871481</v>
+        <v>6.272001329165846</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.52205080255575</v>
+        <v>10.53511705685622</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>18.75051957768725</v>
+        <v>18.76370058698249</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.6460414306354</v>
+        <v>5.659240169590163</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.795916245607472</v>
+        <v>4.809321373260303</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.938989008246409</v>
+        <v>8.952446301956627</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2777199916787936</v>
+        <v>0.2911722803989036</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.553117554646967</v>
+        <v>8.56667360099857</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.240639373946344</v>
+        <v>-4.251069009644496</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>8</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.99343832020989</v>
+        <v>-14.98091603053427</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-29.10501193317423</v>
+        <v>-29.09210212359818</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-29.49988063977082</v>
+        <v>-29.48687350835322</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-29.36962750716332</v>
+        <v>-29.35664836476486</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-29.90804872223549</v>
+        <v>-29.89493791786055</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-17.11060678451983</v>
+        <v>-17.09756388822547</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-17.19534050179211</v>
+        <v>-17.18227424749163</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-17.66252390057353</v>
+        <v>-17.64934289127829</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-17.72352378675583</v>
+        <v>-17.71032504780106</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.278402296101504</v>
+        <v>-6.264945002391286</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.085447582575483</v>
+        <v>6.075017946877331</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-10 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-10 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1304328050036005</v>
+        <v>0.1301137400854557</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.3139333793257677</v>
+        <v>0.3135605564115806</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1277139878238032</v>
+        <v>0.1273843041467799</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2957364400765456</v>
+        <v>0.2953662872497915</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2593101832128326</v>
+        <v>0.2589458144306036</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1547891099083145</v>
+        <v>0.1544517482270109</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2056616981589983</v>
+        <v>0.2053112852551848</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1430995713090297</v>
+        <v>0.1427617286189573</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1445368637698863</v>
+        <v>0.1441981795827161</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1641201084509945</v>
+        <v>0.1637718076175858</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.09546606700109805</v>
+        <v>0.09513327549529293</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1436460594819025</v>
+        <v>0.1433015130666391</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1533517092954355</v>
+        <v>0.1530023162297667</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.123155711860413</v>
+        <v>0.1233655600963388</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1679712411502976</v>
+        <v>0.1675195447304887</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2454933663081462</v>
+        <v>0.2450097541741201</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.06126334445008297</v>
+        <v>0.06082183303204403</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2049717530093105</v>
+        <v>0.204495619456047</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.198019358672255</v>
+        <v>0.1975405038410543</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1142883548830724</v>
+        <v>0.113832263723225</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1170978002809449</v>
+        <v>0.116640136914981</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.03372393946587948</v>
+        <v>0.03328297249260004</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1345009046021062</v>
+        <v>0.1340343696266402</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1377612529630099</v>
+        <v>0.1372870200665233</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.07041193314758942</v>
+        <v>0.0699525031657231</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.06929936878046306</v>
+        <v>0.06884026458863701</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1325626319105808</v>
+        <v>0.1320843722622769</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1243845417842948</v>
+        <v>0.124696641884654</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4017</v>
+        <v>4018</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.06239294529871131</v>
+        <v>0.06187732099132148</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2260875952447279</v>
+        <v>0.2255157424067846</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.04331697691239356</v>
+        <v>0.04278645689870331</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2119468658190442</v>
+        <v>0.211375468402963</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2086924600794617</v>
+        <v>0.2081164650547649</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0229335881509769</v>
+        <v>0.02240630551521861</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.05118037295937938</v>
+        <v>0.05064500716675013</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.004681494409048526</v>
+        <v>-0.005207702411581749</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07234891339327021</v>
+        <v>0.07180271754809553</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08153630551036883</v>
+        <v>0.08097942787297541</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.01513004220704062</v>
+        <v>0.0145874522220808</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01112538409065422</v>
+        <v>-0.01166137739906503</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.08037532944295833</v>
+        <v>0.07981227923344392</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1201749910892147</v>
+        <v>0.1205629941644517</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3976</v>
+        <v>3977</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.176403745470644</v>
+        <v>0.175725573475674</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2079268832751211</v>
+        <v>0.2072210150330562</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.02733280392118331</v>
+        <v>0.02666711351237439</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1461778114518282</v>
+        <v>0.1454835640036336</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1484130092576095</v>
+        <v>0.1477113545930422</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.01723329054392764</v>
+        <v>-0.01789011156297704</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.01216640255135104</v>
+        <v>0.01150085290997538</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.06458316727376712</v>
+        <v>-0.06523543458743575</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01126556017967317</v>
+        <v>-0.01193228034760807</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.01837258987428925</v>
+        <v>-0.01904816465349057</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.01714935004083173</v>
+        <v>0.0164620327846805</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.009730551526224929</v>
+        <v>-0.01041103199113991</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.0870463408196045</v>
+        <v>0.08633609252803609</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1246829950502502</v>
+        <v>0.1251813866559672</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.05758208795328557</v>
+        <v>0.05670192406906693</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2455877095917742</v>
+        <v>0.2446325702793715</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.007792839872919899</v>
+        <v>-0.00869029835067181</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.008723271493813911</v>
+        <v>0.007823304454134927</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1225947915540857</v>
+        <v>0.1216564145366874</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.02540854115066082</v>
+        <v>0.02449944170302842</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.0312818794036005</v>
+        <v>0.03036943066928899</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.140801436990678</v>
+        <v>-0.1416780982277785</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.04232488400073464</v>
+        <v>0.04139997136572759</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.05010454394104613</v>
+        <v>0.04916310883422881</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.03873325377070103</v>
+        <v>0.03779087078701338</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.01077748442129689</v>
+        <v>0.00984235712524395</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.219042524608227</v>
+        <v>0.2180466865202462</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1505870757926928</v>
+        <v>0.1512717851577037</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3839</v>
+        <v>3840</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.02473405777548976</v>
+        <v>0.02362588485625139</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2445076721230919</v>
+        <v>0.243308052933493</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.08429622418640292</v>
+        <v>-0.0854193406045809</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1120560470065897</v>
+        <v>0.1108841027676064</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1335313193445486</v>
+        <v>0.1323418950778716</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1073552638295325</v>
+        <v>0.1061783155167362</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.01084774573778446</v>
+        <v>0.00969351959960818</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.130014147647735</v>
+        <v>-0.1311421632492511</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.0206101551221991</v>
+        <v>-0.02176848083105654</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.02368800379009173</v>
+        <v>-0.02486403143590366</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.00562769953712916</v>
+        <v>-0.006813334423462436</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.01737112419637299</v>
+        <v>0.0161796361692268</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1846845836324462</v>
+        <v>0.1834400680644066</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1105843369385155</v>
+        <v>0.1114762802105744</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.06014728444733919</v>
+        <v>0.05876650914819237</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.182971126645775</v>
+        <v>0.1815152354915313</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.06514407636070985</v>
+        <v>-0.06654529236593021</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1060080860570167</v>
+        <v>0.1045642378297984</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1383088936585466</v>
+        <v>0.1368417431563884</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.07937731722898178</v>
+        <v>0.07793280051625118</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.009138692483006139</v>
+        <v>0.007709854257178961</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1519194467029834</v>
+        <v>-0.1533185074988879</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.0657407053451422</v>
+        <v>-0.06716492054770384</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1054792105106301</v>
+        <v>-0.1069158144306641</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.07606838577705588</v>
+        <v>0.07457754402789618</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.04578977844145982</v>
+        <v>0.04430712183994956</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.277589802197177</v>
+        <v>0.2760338890073939</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1972372798669539</v>
+        <v>0.1983256187646916</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1099063592132197</v>
+        <v>-0.1115686165078174</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.02665970052937183</v>
+        <v>0.02490762721438955</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.272238363348059</v>
+        <v>-0.2739230884128219</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.01885494007196797</v>
+        <v>-0.02060500433125156</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.02687535585561562</v>
+        <v>0.02509461128013157</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.09474022634244506</v>
+        <v>-0.09647928952698948</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1646839635392539</v>
+        <v>-0.1664076893142479</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4542471027445742</v>
+        <v>-0.4559082738068554</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3918191179176915</v>
+        <v>-0.3935000817224577</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3310478314091441</v>
+        <v>-0.3327737029800844</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1947521059873552</v>
+        <v>-0.196522520718645</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.253799089856237</v>
+        <v>-0.2555532704595649</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.08818679317914757</v>
+        <v>-0.09000050693526163</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2036255351196203</v>
+        <v>-0.2021559661662309</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3561</v>
+        <v>3562</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.08070829422762671</v>
+        <v>0.07852452890620754</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.004816019376299607</v>
+        <v>-0.007043365903719234</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3845390944180735</v>
+        <v>-0.3866775945552874</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.01289839594505082</v>
+        <v>0.01065286703805413</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.02192326656003019</v>
+        <v>0.01965183290953831</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1976059439482398</v>
+        <v>-0.1998047845840105</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.3231431923750705</v>
+        <v>-0.3253115128320729</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6349096589139478</v>
+        <v>-0.6370110527133548</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7086611956173741</v>
+        <v>-0.7107455692477416</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7019799675762712</v>
+        <v>-0.7041025093020608</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.6106132949790819</v>
+        <v>-0.6127710893477243</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.5886725207374681</v>
+        <v>-0.590836210305234</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.459894187657099</v>
+        <v>-0.462112595294272</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.7279475311567012</v>
+        <v>-0.7259365730553782</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2319851541755398</v>
+        <v>-0.2347083292508074</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1645565916681022</v>
+        <v>-0.1673866289964892</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4852820996248397</v>
+        <v>-0.4880410506766282</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2224312454810828</v>
+        <v>-0.2252615034509873</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.01468033193459206</v>
+        <v>-0.01760146926241646</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4317640025210068</v>
+        <v>-0.4345489890142531</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5006605836395224</v>
+        <v>-0.5034314654928096</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8350385204566564</v>
+        <v>-0.8377380973584607</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9678934854982373</v>
+        <v>-0.9705589659298042</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9536957827844219</v>
+        <v>-0.9564123144439662</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.8496636364584589</v>
+        <v>-0.8524230597346758</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.7990542675616084</v>
+        <v>-0.8018281903929179</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6174216267140693</v>
+        <v>-0.6202727384780928</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9371066060596362</v>
+        <v>-0.934498890604452</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3450611950167755</v>
+        <v>-0.3486539786184082</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.05430073960589965</v>
+        <v>-0.05809903240807301</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3705889602162316</v>
+        <v>-0.3743193957991053</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4092314675593585</v>
+        <v>-0.4129428281115963</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3119484436839599</v>
+        <v>-0.3157299970684662</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.7096779919501728</v>
+        <v>-0.7133175248704617</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.8396576278373331</v>
+        <v>-0.8432649595659356</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.042325635393937</v>
+        <v>-1.045905294499178</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.365451273585784</v>
+        <v>-1.368937191543402</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.299935394598471</v>
+        <v>-1.303503837933306</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.115611598427009</v>
+        <v>-1.119253743866715</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.281239982428446</v>
+        <v>-1.284830415927352</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.125955412747736</v>
+        <v>-1.129625891934893</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.541802572607722</v>
+        <v>-1.538230579340564</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.099732260618417</v>
+        <v>-0.1047446784593902</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.08625774697195254</v>
+        <v>-0.09143255546962337</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3290263684140413</v>
+        <v>-0.3341608492775308</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3146677216405251</v>
+        <v>-0.3197974434918294</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3656417493893684</v>
+        <v>-0.3708092315334781</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5864619153045325</v>
+        <v>-0.5915296944608031</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7872559664012968</v>
+        <v>-0.7922675405835236</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.068564169029983</v>
+        <v>-1.073529405870786</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.379952118410834</v>
+        <v>-1.384821692096452</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.439666433167318</v>
+        <v>-1.444601010965521</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.155795645110487</v>
+        <v>-1.160848293190398</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.270900859186099</v>
+        <v>-1.275914515470873</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.000408203482408</v>
+        <v>-1.00555641302671</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.438089740894675</v>
+        <v>-1.433385414467296</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4845920245962674</v>
+        <v>-0.4912329059949343</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2460205152033481</v>
+        <v>0.2388967706148648</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.05502634246355598</v>
+        <v>-0.06209474729127606</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.09531714228316446</v>
+        <v>0.08820593254240805</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.09077297472718016</v>
+        <v>-0.09788994738084256</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1054369174592651</v>
+        <v>-0.1125140543384191</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.428624580107595</v>
+        <v>-0.435597733459133</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4525128181945917</v>
+        <v>-0.4393318088993539</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9937491284625963</v>
+        <v>-0.9805503895078331</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.158645276292333</v>
+        <v>-1.165526444795951</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6406943478574192</v>
+        <v>-0.6477979218294863</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8446108547323234</v>
+        <v>-0.8516389387604661</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.467455399719384</v>
+        <v>-0.4746822003907099</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9741379096525833</v>
+        <v>-0.9680823120942676</v>
       </c>
     </row>
     <row r="19">
@@ -2890,153 +2890,153 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3905391777028342</v>
+        <v>-0.3992833774731253</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3476024459107308</v>
+        <v>0.3382776232372606</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.26105111339632</v>
+        <v>0.2516885831500559</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.9451721657720782</v>
+        <v>0.935546159141964</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6338735681530565</v>
+        <v>0.6242771271108296</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7903752122068397</v>
+        <v>0.7807592201589841</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3599194245279875</v>
+        <v>0.3504589767309483</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3430020920583985</v>
+        <v>0.3561831013536363</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1273305816801837</v>
+        <v>-0.1141318427254205</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1997234703511737</v>
+        <v>-0.1863183426983426</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.250455665421299</v>
+        <v>0.2639129591315168</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.2472938010564363</v>
+        <v>-0.2338415123363262</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.05153296610582458</v>
+        <v>0.04187337319594064</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.4538805616277983</v>
+        <v>-0.4462760744167795</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0001786</t>
+          <t>X &gt; -0.0001787</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4535471144076197</v>
+        <v>-0.4646042951469553</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3167567743087645</v>
+        <v>0.3049966977980105</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4456728992491392</v>
+        <v>0.4337614122817044</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9640084438126237</v>
+        <v>0.9518815807886867</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4961292977463359</v>
+        <v>0.4840906795066786</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4552723613229688</v>
+        <v>0.4433080463794425</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1953405017921028</v>
+        <v>-0.2070357195497863</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.07161480966451705</v>
+        <v>-0.05843380036927925</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1780692413013725</v>
+        <v>-0.1648705023466093</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2100126081474798</v>
+        <v>-0.1966074804946487</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1306886129894878</v>
+        <v>0.1441459066997055</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2440191387559807</v>
+        <v>-0.2305668500358706</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.138580252656773</v>
+        <v>-0.1507177033492937</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2726051926748241</v>
+        <v>-0.263090284136851</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0007171</t>
+          <t>X &gt; 0.000717</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5526824468698379</v>
+        <v>-0.5666740703505795</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2639201056607163</v>
+        <v>0.2490623299258203</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3058453315993219</v>
+        <v>0.2908474931797471</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.719886559332835</v>
+        <v>0.7047013284866779</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.05612732689449729</v>
+        <v>0.0411234632136086</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.02328978486060151</v>
+        <v>0.008372652204421627</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3920618132675173</v>
+        <v>-0.4068006171792931</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1420320972949156</v>
+        <v>-0.1288510879996778</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.04934345888706559</v>
+        <v>-0.03614471993230239</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.07389201182272132</v>
+        <v>0.0872971394755524</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4838927858657982</v>
+        <v>0.497350079576016</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.004437684127125863</v>
+        <v>0.009118362224477039</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.01804624992547588</v>
+        <v>0.0299359796641312</v>
       </c>
     </row>
     <row r="22">
@@ -3046,101 +3046,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8140040243938245</v>
+        <v>-0.8319172083906565</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7298937272031196</v>
+        <v>0.7104906872444872</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4853700976923108</v>
+        <v>0.4659566803260233</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9432414420692652</v>
+        <v>0.9235876234357292</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1421580113734819</v>
+        <v>0.1227716453035583</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4130338774187052</v>
+        <v>0.3935760999611873</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.05311696542309363</v>
+        <v>-0.07234516947745107</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.2484755080603307</v>
+        <v>0.2616565173555685</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.04907080035733458</v>
+        <v>-0.03587206140257138</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2835361257915636</v>
+        <v>0.2969412534443947</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5518756459447047</v>
+        <v>0.5653329396549225</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.05402935326057445</v>
+        <v>0.06748164198068451</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.0705422298901226</v>
+        <v>-0.0569861835385197</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2607062635784487</v>
+        <v>-0.2452067722238738</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002509</t>
+          <t>X &gt; 0.002508</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1416</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7353511190847968</v>
+        <v>-0.7592013432539559</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.278520790259968</v>
+        <v>1.25248296782236</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.486034853186929</v>
+        <v>1.459643029296316</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.373853817713353</v>
+        <v>1.347576987347821</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3810909110508334</v>
+        <v>0.355238262548184</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.999837816750464</v>
+        <v>0.973663192169461</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.03629791628699053</v>
+        <v>0.01073916111810291</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4165721446241264</v>
+        <v>0.4297531539193642</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1437078516621639</v>
+        <v>0.1569065906169271</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2116617626794408</v>
+        <v>0.2250668903322719</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.501258720847737</v>
+        <v>0.5147160145579548</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1825345335603927</v>
+        <v>0.1959868222805028</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1670986084579482</v>
+        <v>-0.1535425621063453</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.05862021403476803</v>
+        <v>-0.06904984973292017</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1140</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5283728180265683</v>
+        <v>-0.561195262646045</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9649181367558413</v>
+        <v>0.9297319375371842</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.755587426720865</v>
+        <v>1.719420197940487</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.147009970945255</v>
+        <v>1.111418126923681</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1313903662833482</v>
+        <v>0.09630551471388316</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.003428303199463</v>
+        <v>0.9677297138779508</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.04150160347105469</v>
+        <v>0.05456785777153073</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4515111871456838</v>
+        <v>0.4646921964409216</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3989623832471381</v>
+        <v>-0.3857636442923749</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1964559893277027</v>
+        <v>-0.1830508616748716</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5637029670564715</v>
+        <v>0.5771602607666892</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2791068580542344</v>
+        <v>-0.2656545693341243</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6116421707535267</v>
+        <v>-0.5980861244019238</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8005173297053076</v>
+        <v>-0.8109469654034598</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>907</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.616245337753831</v>
+        <v>-1.659448341596779</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.0113437199542048</v>
+        <v>-0.03508457973853041</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8847347448445646</v>
+        <v>0.8369464696928901</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.7458840439917935</v>
+        <v>0.6982966901802001</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.273687488755314</v>
+        <v>-1.319580382106977</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.255590246482349</v>
+        <v>-0.3024097032034447</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.7813382967204419</v>
+        <v>-0.7682720424199658</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4052820531198833</v>
+        <v>0.4184630624151211</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.86850724871843</v>
+        <v>-0.8553085097636668</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9468573510561598</v>
+        <v>-0.9334522234033287</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.06117874028225856</v>
+        <v>0.07463603399247631</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3454524353381245</v>
+        <v>-0.3320001466180145</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5451998798001156</v>
+        <v>-0.5316438334485127</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1852249642823693</v>
+        <v>-0.1956545999805215</v>
       </c>
     </row>
     <row r="26">
@@ -3257,98 +3257,98 @@
         <v>692</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.3844134823596335</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.216827147285535</v>
+        <v>2.148930874967093</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.910191302675216</v>
+        <v>2.840712698543335</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.826337910704112</v>
+        <v>1.758459548904199</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6511944653812307</v>
+        <v>-0.7162635662755434</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5917053542084929</v>
+        <v>0.5250912344296523</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5045890567054059</v>
+        <v>-0.4915228024049298</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.617822920235632</v>
+        <v>0.6310039295308698</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1657203185478267</v>
+        <v>-0.1525215795930634</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7268281625352842</v>
+        <v>-0.7134230348824531</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.07997920678875658</v>
+        <v>0.09343650049897434</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6081809884669696</v>
+        <v>-0.5947286997468595</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.416651105790443</v>
+        <v>0.4302071521420459</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.3773550970262676</v>
+        <v>0.3669254613281154</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.006092</t>
+          <t>X &gt; 0.006091</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>546</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.041951879427046</v>
+        <v>2.953866578161303</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.349533521371228</v>
+        <v>3.258170108706722</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.241467265511517</v>
+        <v>3.14949012801042</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.747160814004566</v>
+        <v>2.656102090608549</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.667819650707834</v>
+        <v>0.579514636883971</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.349100175187125</v>
+        <v>2.258011980147479</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.081216274764664</v>
+        <v>2.09428252906514</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.896084158034455</v>
+        <v>2.909265167329693</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.553032989800862</v>
+        <v>1.566231728755625</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1534572553223867</v>
+        <v>0.1668623829752178</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.230755213056085</v>
+        <v>1.244212506766303</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.3493874546506035</v>
+        <v>0.3628397433707136</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.028033942606797</v>
+        <v>1.0415899889584</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.9114549085827193</v>
+        <v>0.9010252728845671</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>410</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.612841873026738</v>
+        <v>1.494987583923482</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.24849896270954</v>
+        <v>4.120458262875253</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.885107253691643</v>
+        <v>2.898114385109245</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.698333657885222</v>
+        <v>1.575555025065647</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1635231747902353</v>
+        <v>-0.2832874324236627</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.218661508163088</v>
+        <v>2.093433678684505</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.133927790890809</v>
+        <v>2.146994045191285</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.374061465280043</v>
+        <v>3.387242474575281</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.361842066902618</v>
+        <v>1.375040805857381</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2678144428503018</v>
+        <v>0.2812195705031328</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.526475752679062</v>
+        <v>1.53993304638928</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.09744427587815352</v>
+        <v>0.1108965645982636</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.628409177128376</v>
+        <v>1.641965223479978</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4147158752583167</v>
+        <v>0.4042862395601645</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>306</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.40266557589392</v>
+        <v>1.240766817362079</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.687195859033565</v>
+        <v>3.700105668609616</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.668950529060346</v>
+        <v>1.681957660477948</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.47452833699252</v>
+        <v>1.487507479390985</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1849216864048699</v>
+        <v>-0.3494833724060129</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2913539997938983</v>
+        <v>0.1255631476051562</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.840607210626189</v>
+        <v>1.853673464926665</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.35381596870743</v>
+        <v>2.366996978002668</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.9856265400414728</v>
+        <v>0.998825278996236</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.7890961262553731</v>
+        <v>0.8025012539082041</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.545127115663291</v>
+        <v>2.558584409373509</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.599118116145981</v>
+        <v>1.612570404866091</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.466445204547476</v>
+        <v>3.480001250899079</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.75538222309828</v>
+        <v>1.744952587400128</v>
       </c>
     </row>
     <row r="30">
@@ -3465,98 +3465,98 @@
         <v>236</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.780823283165553</v>
+        <v>2.56110077618834</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.388658952901714</v>
+        <v>5.401568762477766</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.306026533224966</v>
+        <v>3.319033664642568</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.170456881022332</v>
+        <v>2.183436023420796</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3662128811400365</v>
+        <v>0.3793236855149758</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.4741389781920304</v>
+        <v>0.2547567868800158</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.660591701597724</v>
+        <v>1.6736579558982</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.312052370612832</v>
+        <v>3.32523337990807</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.979866043752565</v>
+        <v>1.993064782707329</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.129740858724638</v>
+        <v>1.143145986377469</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.738546856440955</v>
+        <v>4.752004150151173</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.230557132430455</v>
+        <v>2.244009421150565</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.505217775722834</v>
+        <v>3.518773822074436</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.636295040202519</v>
+        <v>1.625865404504367</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.009675</t>
+          <t>X &gt; 0.009674</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>184</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.854387766746541</v>
+        <v>1.866910056422164</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.590640240738814</v>
+        <v>4.603550050314865</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.478380229794396</v>
+        <v>1.491387361211999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.195714463685064</v>
+        <v>-2.1827353212866</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.647179157018094</v>
+        <v>-1.634068352643155</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.436693741041573</v>
+        <v>-2.423650844747208</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3475144148355938</v>
+        <v>-0.3344481605351177</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8157369689916081</v>
+        <v>0.8289179782868459</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.419175960668959</v>
+        <v>-1.405977221714195</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.6388663630881837</v>
+        <v>-0.6254612354353526</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.417249877811628</v>
+        <v>2.430707171521846</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.352714790929902</v>
+        <v>-1.339262502209792</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1425346192661081</v>
+        <v>-0.1289785729145052</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.9797698087289461</v>
+        <v>-0.9901994444270983</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.747940990134857</v>
+        <v>4.76046327981048</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.515677721998173</v>
+        <v>4.528587531574225</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.775742708736338</v>
+        <v>-2.762735577318736</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.335144748542632</v>
+        <v>-3.322165606144168</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.563221136028595</v>
+        <v>-4.550110331653656</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.955434370726728</v>
+        <v>-4.942391474432362</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.591892225930046</v>
+        <v>-1.57882597162957</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6797652798839593</v>
+        <v>-0.6665842705887215</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.189041028135222</v>
+        <v>-4.175842289180459</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.280545523507982</v>
+        <v>-2.267140395855151</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.652632186657208</v>
+        <v>1.666089480367425</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.45091569048013</v>
+        <v>-2.43746340176002</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.802204784183651</v>
+        <v>-0.7886487378320481</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.000759313976324</v>
+        <v>-4.011188949674477</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>115</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.63699646239872</v>
+        <v>6.649518752074343</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.416727197260549</v>
+        <v>2.4296370068366</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.325967596292564</v>
+        <v>-2.312960464874962</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.54354055064158</v>
+        <v>-6.530561408243116</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-7.951526983105055</v>
+        <v>-7.938416178730115</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.914954610606785</v>
+        <v>-5.901911714312419</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.390992675705149</v>
+        <v>-3.377926421404673</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.988610857095352</v>
+        <v>-2.975429847800115</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-8.267002047625475</v>
+        <v>-8.253803308670712</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.508431580479488</v>
+        <v>-6.495026452826657</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.495793600449247</v>
+        <v>-1.482336306739029</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.678801747451637</v>
+        <v>-6.665349458731527</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.62079548883132</v>
+        <v>-3.607239442479717</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.849335026120251</v>
+        <v>-6.859764661818403</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.202213853703071</v>
+        <v>6.214736143378694</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.416727197260549</v>
+        <v>2.4296370068366</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.325967596292564</v>
+        <v>-2.312960464874962</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-5.456584028902455</v>
+        <v>-5.443604886503991</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-8.168918287452883</v>
+        <v>-8.155807483077943</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.958432871476354</v>
+        <v>-8.945389975181989</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.869253545270368</v>
+        <v>-6.856187290969892</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.423393465791001</v>
+        <v>-8.410212456495763</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.74526291719069</v>
+        <v>-11.73206417823593</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-9.33451853700123</v>
+        <v>-9.321113409348399</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.104489252623161</v>
+        <v>-4.091031958912943</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.417932182234246</v>
+        <v>-8.404479893514136</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.501508939163735</v>
+        <v>-7.511938574861887</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>8.220847394075733</v>
+        <v>8.233369683751356</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.418797590635293</v>
+        <v>5.431707400211344</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.179151316687133</v>
+        <v>-3.166172174288668</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.098524912711682</v>
+        <v>-6.085414108336742</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-8.1820353559484</v>
+        <v>-8.168992459654035</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-5.8858166922683</v>
+        <v>-5.872750437967824</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-7.543476281525997</v>
+        <v>-7.530295272230759</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-11.17590473913687</v>
+        <v>-11.16270600018211</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-9.645077543212409</v>
+        <v>-9.631672415559578</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-3.897449915149032</v>
+        <v>-3.883992621438814</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-9.815447710184557</v>
+        <v>-9.801995421464447</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.805934434075141</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-10 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-10 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.24786907603138</v>
+        <v>-11.23495926645533</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-11.51248465002047</v>
+        <v>-11.499505507622</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.669953484140251</v>
+        <v>-9.656842679765312</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.420130594043641</v>
+        <v>-3.407087697749276</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4616190248511458</v>
+        <v>-0.4484202858963826</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.311744209879073</v>
+        <v>-1.298339082226242</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2916381863750317</v>
+        <v>-0.2781858976549216</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>123</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.338966775494526</v>
+        <v>-5.326444485818904</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.324524128296183</v>
+        <v>-5.311614318720132</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.8413440544049635</v>
+        <v>-0.8283369229873614</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.776131572203973</v>
+        <v>-4.763152429805508</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.501544657194842</v>
+        <v>-4.488433852819902</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.9520701991539724</v>
+        <v>-0.939027302859607</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.223795786344958</v>
+        <v>-0.210729532044482</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.56105333519875</v>
+        <v>2.574234344493988</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.06102905877254727</v>
+        <v>0.07422779772731047</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.02391200382592018</v>
+        <v>0.03731713147875126</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.258183069752235</v>
+        <v>2.271640363462453</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.292566227097666</v>
+        <v>2.306018515817776</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2462953559901635</v>
+        <v>0.2598514023417664</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.496016688266451</v>
+        <v>0.4855870525682988</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>151</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.500060836766259</v>
+        <v>-1.487538547090637</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.773886105359658</v>
+        <v>-3.760976295783607</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1952448781814198</v>
+        <v>-0.1822377467638177</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.038501679348748</v>
+        <v>-4.025522536950284</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.914671238791776</v>
+        <v>-3.901560434416837</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.680783943956989</v>
+        <v>1.693826840251354</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.59605022668471</v>
+        <v>1.609116480985186</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.115621794790627</v>
+        <v>3.128802804085865</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.730118597350049</v>
+        <v>1.743317336304813</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.542245067951256</v>
+        <v>1.555650195604088</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.324246710521102</v>
+        <v>3.33770400423132</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.020881523495667</v>
+        <v>4.034333812215777</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.613871945663348</v>
+        <v>1.627427992014951</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.5390899666813596</v>
+        <v>0.5286603309832074</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>192</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.535104986876647</v>
+        <v>-3.522582697201024</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.542511933174232</v>
+        <v>-2.529602123598181</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1876193602291778</v>
+        <v>0.2006264916467799</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.765460840496658</v>
+        <v>-1.752481698098194</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.783048722235492</v>
+        <v>-1.769937917860553</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.160226548813505</v>
+        <v>2.17326944510787</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.075492831541226</v>
+        <v>2.088559085841702</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.691642766093054</v>
+        <v>3.704823775388292</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>3.123008285532187</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.30135102821616</v>
+        <v>3.314756155868992</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.575764370565246</v>
+        <v>2.589221664275463</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.130980861244012</v>
+        <v>3.144433149964122</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.148226250299111</v>
+        <v>1.161782296650713</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3562809159087337</v>
+        <v>0.3458512802105815</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>261</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7693003891754913</v>
+        <v>-0.7567780994998685</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.380874002139748</v>
+        <v>-2.367964192563697</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6725331533326226</v>
+        <v>0.6855402847502248</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.8027862859401225</v>
+        <v>0.8157654283385867</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8850602164883625</v>
+        <v>-0.8719494121134233</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.243356816215545</v>
+        <v>1.256423070516021</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.841307517050907</v>
+        <v>3.854488526346145</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.481457056155968</v>
+        <v>1.494655795110731</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.397615396032251</v>
+        <v>1.411020523685082</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.576003834166784</v>
+        <v>1.589461127877001</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.99352875396432</v>
+        <v>2.00698104268443</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.108718194145332</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.09271333696483453</v>
+        <v>-0.1031429726629867</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>329</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2138030618513156</v>
+        <v>-0.2012807721756928</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.825376674815573</v>
+        <v>-1.812466865239521</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.427171031961699</v>
+        <v>1.440178163379301</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5702354098988778</v>
+        <v>-0.5572562675004136</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.8047052571898945</v>
+        <v>-0.7915944528149552</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.203311951693081</v>
+        <v>-0.1902690553987156</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.231711169940411</v>
+        <v>1.244777424240887</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.892187345627001</v>
+        <v>2.905368354922238</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.981062274416772</v>
+        <v>1.994467402069603</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.776308950099192</v>
+        <v>1.78976624380941</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.506740739663471</v>
+        <v>1.520193028383581</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4332707101872089</v>
+        <v>-0.419714663835606</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.424353357651384</v>
+        <v>0.4139237219532319</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>402</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.5033885689661943</v>
+        <v>-0.4908662792905716</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8711810874030874</v>
+        <v>-0.8582712778270363</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9727561761495735</v>
+        <v>0.9857633075671757</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3895280046757534</v>
+        <v>-0.3765488622772892</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.67919300084246</v>
+        <v>-0.6660821964675208</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1157613746841406</v>
+        <v>0.128804270978506</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.026052533033763</v>
+        <v>1.039118787334239</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.548918885496043</v>
+        <v>2.562099894791281</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.990406561502787</v>
+        <v>2.003605300457551</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.384062471002224</v>
+        <v>2.397467598655055</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.686771833251818</v>
+        <v>0.7002291269620358</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.9699112095027118</v>
+        <v>0.9833634982228219</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.191636933780494</v>
+        <v>-1.178080887428891</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4444031636932664</v>
+        <v>-0.4548327993914185</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>489</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8807948086243869</v>
+        <v>0.8933170983000096</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.496215060690794</v>
+        <v>0.5091248702668452</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.350835106650443</v>
+        <v>2.363842238068045</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6405974417119324</v>
+        <v>0.6535765841103967</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3066752041448808</v>
+        <v>0.3197860085198201</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.422113051880984</v>
+        <v>1.43515594817535</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.155375244629155</v>
+        <v>2.168441498929631</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.346678553414122</v>
+        <v>4.35985956270936</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.08117968972671</v>
+        <v>4.094378428681473</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.640052459708997</v>
+        <v>3.653457587361828</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.617303225370975</v>
+        <v>2.630760519081193</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.060684337726634</v>
+        <v>3.074136626446744</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.822433816761283</v>
+        <v>1.835989863112886</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.685652081552902</v>
+        <v>2.67522244585475</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>607</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4341302477223365</v>
+        <v>-0.4216079580467138</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5902104720975956</v>
+        <v>0.6031202816736467</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.501766806687172</v>
+        <v>2.514773938104774</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3255948981085055</v>
+        <v>0.3385740405069697</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2814076204333702</v>
+        <v>0.2945184248083095</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.732062078742118</v>
+        <v>1.745104975036483</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.6357962362639</v>
+        <v>2.648862490564376</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.475037878668566</v>
+        <v>4.488218887963804</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.07301657568231</v>
+        <v>5.086215314637073</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.046614619649439</v>
+        <v>5.06001974730227</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.512372003733844</v>
+        <v>4.525829297444062</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.38201051528025</v>
+        <v>4.39546280400036</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.632266612737332</v>
+        <v>3.645822659088935</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.199945111405711</v>
+        <v>5.189515475707559</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>754</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.087463536553955</v>
+        <v>1.099985826229577</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.200027854624174</v>
+        <v>1.212937664200226</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.396671084367114</v>
+        <v>2.409678215784716</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.333290264719963</v>
+        <v>1.346269407118427</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.396991065562915</v>
+        <v>0.4101018699378542</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.41857093431306</v>
+        <v>2.431613830607425</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.864341195820622</v>
+        <v>2.877407450121098</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.386547717463522</v>
+        <v>4.399728726758759</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.121303799450985</v>
+        <v>5.134502538405748</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.066934582592822</v>
+        <v>5.080339710245653</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.596929268885319</v>
+        <v>4.610386562595536</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.366060436840833</v>
+        <v>4.379512725560943</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.547927841811045</v>
+        <v>3.561483888162648</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.991283126341969</v>
+        <v>4.980853490643817</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>946</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.206350263299534</v>
+        <v>1.218872552975157</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5461508575234362</v>
+        <v>0.5590606670994873</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.419781093844399</v>
+        <v>1.432788225262001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.655742471695028</v>
+        <v>1.668721614093492</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.328737747109123</v>
+        <v>1.341848551484063</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.788970382499194</v>
+        <v>2.802013278793559</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.338486136685695</v>
+        <v>3.351552390986171</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.034093435578612</v>
+        <v>4.04727444487385</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.241592492313849</v>
+        <v>5.254791231268612</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.025716778744709</v>
+        <v>5.03912190639754</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.398130473454607</v>
+        <v>4.411587767164825</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.961054857015689</v>
+        <v>4.974507145735799</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.435092000827659</v>
+        <v>4.448648047179262</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.847604030778349</v>
+        <v>5.837174395080197</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1194</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2703807752674052</v>
+        <v>0.282903064943028</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5013532259547446</v>
+        <v>0.5142630355307958</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.944005457381607</v>
+        <v>0.9570125887992091</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9905064961867609</v>
+        <v>1.003485638585225</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.122102031533359</v>
+        <v>1.135212835908298</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.754552344458396</v>
+        <v>1.767595240752762</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.339835377604871</v>
+        <v>2.352901631905347</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.045181292056199</v>
+        <v>3.058362301351437</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.905454437699696</v>
+        <v>3.918653176654459</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.060354378299913</v>
+        <v>4.073759505952744</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.353088491168265</v>
+        <v>3.366545784878483</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.638727929920726</v>
+        <v>3.652180218640837</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.967217037568794</v>
+        <v>2.980773083920397</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.054459307868527</v>
+        <v>4.044029672170375</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1466</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9125562301987458</v>
+        <v>0.9250785198743685</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2221781457082912</v>
+        <v>-0.2092683361322401</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2003918397932054</v>
+        <v>0.2133989712108075</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.009954482640161189</v>
+        <v>0.003024659758303017</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3371828853939363</v>
+        <v>0.3502936897688755</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4302651500850772</v>
+        <v>0.4433080463794425</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.094850233902712</v>
+        <v>1.107916488203188</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.14286123916736</v>
+        <v>1.117687081473676</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.21167403043372</v>
+        <v>2.185721305300419</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.521166853591332</v>
+        <v>2.534571981244163</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.566072465153695</v>
+        <v>1.579529758863913</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.941519742553695</v>
+        <v>1.954972031273805</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.248413835565145</v>
+        <v>1.261969881916748</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.180263407950569</v>
+        <v>2.169833772252417</v>
       </c>
     </row>
     <row r="19">
@@ -4587,150 +4587,150 @@
         <v>1727</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.566607869166468</v>
+        <v>0.5791301588420907</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.2943883765922521</v>
+        <v>-0.281478567016201</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2851000393089222</v>
+        <v>-0.2720929078913201</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.194107876678331</v>
+        <v>-1.181128734279866</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.7510048423278732</v>
+        <v>-0.737894037952934</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9154566690463852</v>
+        <v>-0.9024137727520198</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2496130191131272</v>
+        <v>-0.2365467648126511</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2231824794297594</v>
+        <v>-0.2417216441652172</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4990195658452521</v>
+        <v>0.4800273496569716</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6065129715359987</v>
+        <v>0.5871549997996297</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>-0.04747825860867039</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6754944686557138</v>
+        <v>0.6560072240381913</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2552398577108121</v>
+        <v>0.268795904062415</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9681922264665346</v>
+        <v>0.9577625907683824</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0001786</t>
+          <t>X &lt; -0.0001787</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1970</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5192199076381243</v>
+        <v>0.5317421973137471</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1809613002628438</v>
+        <v>-0.1680514906867927</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4239312726822178</v>
+        <v>-0.4109241412646156</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9519059881759873</v>
+        <v>-0.9389268457775231</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4270360640076447</v>
+        <v>-0.4139252596327054</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3321257718615982</v>
+        <v>-0.3190828755672328</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4439000045369994</v>
+        <v>0.4569662588374754</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.308600719487174</v>
+        <v>0.2936950834051686</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.4784528984949716</v>
+        <v>0.4634338174470756</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5186431174656576</v>
+        <v>0.5033648735577856</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1396596014125322</v>
+        <v>0.1245073302659989</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5580113180968027</v>
+        <v>0.5426447176962412</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4423252350706832</v>
+        <v>0.4558812814222861</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5905237247073813</v>
+        <v>0.5800940890092292</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0007171</t>
+          <t>X &lt; 0.000717</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2217</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4980146712430198</v>
+        <v>0.5105369609186425</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.07892106497810403</v>
+        <v>-0.06601125540205288</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2038842385112645</v>
+        <v>-0.1908771070936623</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.062711511682636</v>
+        <v>0.07582231605757528</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1352321718454377</v>
+        <v>0.1482750681398031</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5453252651894474</v>
+        <v>0.5583915194899234</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3280251543318826</v>
+        <v>0.3162441532560436</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2920097566929769</v>
+        <v>0.2802240071043443</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1876122894774213</v>
+        <v>0.1756859172377432</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.1720480824916848</v>
+        <v>-0.1838639213101132</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2483162985749416</v>
+        <v>0.2363101215729628</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2594971118236913</v>
+        <v>0.2473886988148308</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2385824495127054</v>
+        <v>0.2281528138145532</v>
       </c>
     </row>
     <row r="22">
@@ -4743,98 +4743,98 @@
         <v>2478</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5661430002409134</v>
+        <v>0.5786652899165361</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3610505805172224</v>
+        <v>-0.3481407709411712</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2728274996742073</v>
+        <v>-0.2598203682566051</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5451508565997187</v>
+        <v>-0.5321717142012545</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.003384450067244416</v>
+        <v>0.01649525444218369</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1420077507034065</v>
+        <v>-0.1289648544090412</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.2160926705106263</v>
+        <v>0.2291589248111023</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.01266740027213586</v>
+        <v>0.003636174744173104</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.255928268038609</v>
+        <v>0.2467832888883379</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.03275973438302771</v>
+        <v>0.02355954023644102</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1493700380369063</v>
+        <v>-0.1585362962243337</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1900268475288129</v>
+        <v>0.1807234725447628</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2768077676518104</v>
+        <v>0.2673944386434499</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4054637246254416</v>
+        <v>0.3950340889272894</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002509</t>
+          <t>X &lt; 0.002508</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3880404764554868</v>
+        <v>0.4005627661311095</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5348778266138794</v>
+        <v>-0.5219680170378282</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.712276435348933</v>
+        <v>-0.6992693039313309</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6182683190516869</v>
+        <v>-0.6052891766532227</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1055840611263932</v>
+        <v>-0.0924732567514539</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3880623843748552</v>
+        <v>-0.3750194880804898</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1433691756272424</v>
+        <v>0.1564354299277184</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.05012361050834357</v>
+        <v>-0.05691809968721628</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1264943488987882</v>
+        <v>0.1196241907775288</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.09471097016100316</v>
+        <v>0.08774309819761328</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.05335692405059689</v>
+        <v>-0.06030059019961698</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1103744705395826</v>
+        <v>0.1033714439750071</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.291774197992531</v>
+        <v>0.2846490359390188</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2351568849009738</v>
+        <v>0.2404738132048863</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.2074839459296882</v>
+        <v>0.220006235605311</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2512569924627712</v>
+        <v>-0.2383471828867201</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6131876226430251</v>
+        <v>-0.6001804912254229</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3511821843701739</v>
+        <v>-0.3382030419717097</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.03266274021510895</v>
+        <v>0.04577354459004823</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2627806975633149</v>
+        <v>-0.2497378012689495</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1316776201189285</v>
+        <v>0.1266849092936084</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.02079680762700775</v>
+        <v>-0.02578440692911954</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.332031768799645</v>
+        <v>0.3269195138336514</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2588048540736807</v>
+        <v>0.2536368020938511</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.02634027036733499</v>
+        <v>-0.03143576756270505</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.290634326590542</v>
+        <v>0.2854344696605935</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.417271314676789</v>
+        <v>0.4119885672777741</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4876932893125172</v>
+        <v>0.4914920307333048</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4585347602427632</v>
+        <v>0.4710570499183859</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1011673265382171</v>
+        <v>0.1140771361142683</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2019301962100926</v>
+        <v>-0.1889230647924904</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1328578528347819</v>
+        <v>-0.1198787104363177</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4299751382723116</v>
+        <v>0.4430859426472509</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1767899728983409</v>
+        <v>0.1898328691927063</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.3536191065310206</v>
+        <v>0.3498456668552663</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.0257221967633896</v>
+        <v>0.02201573785259114</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.410279030145503</v>
+        <v>0.4064487507908296</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4347736928409773</v>
+        <v>0.4308767927336561</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1554212333103422</v>
+        <v>0.1515940481447871</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2683927521419633</v>
+        <v>0.2645311891798059</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3253031969576057</v>
+        <v>0.3213938504355767</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2245153531979085</v>
+        <v>0.2273784618987094</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0824165062030886</v>
+        <v>-0.06989421652746586</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3449660089491999</v>
+        <v>-0.3320561993731488</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5389162310452207</v>
+        <v>-0.5259090996276186</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2938525358659589</v>
+        <v>-0.2808733934674947</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2010213122076721</v>
+        <v>0.2141321165826113</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.01818428164956742</v>
+        <v>-0.005141385355202033</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2285756624341317</v>
+        <v>0.2258773024509608</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.006918948363775712</v>
+        <v>0.004260324340343402</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.1915868136462748</v>
+        <v>0.1888708166445667</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3056613730437405</v>
+        <v>0.3028702035564379</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.145857548681569</v>
+        <v>0.1431009746202889</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2827203667069185</v>
+        <v>0.2799246705160101</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.08004606623238431</v>
+        <v>0.07728689699574431</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.08717370455468654</v>
+        <v>0.08925435757613087</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.006092</t>
+          <t>X &lt; 0.006091</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4548708270970252</v>
+        <v>-0.4423485374214025</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4135518780778114</v>
+        <v>-0.4006420685017602</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.450293862911316</v>
+        <v>-0.4372867314937139</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3475889396702101</v>
+        <v>-0.3346097972717459</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.03201566438425374</v>
+        <v>-0.01890486000931446</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2579897046300204</v>
+        <v>-0.244946808335655</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1899671206953855</v>
+        <v>-0.191916120769875</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3113662379495707</v>
+        <v>-0.3132999042296021</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.08153316089431684</v>
+        <v>-0.08353342707346911</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.131535804829511</v>
+        <v>0.1294446036219554</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.03012643403245363</v>
+        <v>-0.03218162677067937</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1025592276899303</v>
+        <v>0.1004676327227472</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.00147286912328326</v>
+        <v>-0.000607328073343183</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.01835757705358532</v>
+        <v>0.01995308350435465</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3758</v>
+        <v>3759</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1706350284658811</v>
+        <v>-0.1581127387902583</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3752535047165679</v>
+        <v>-0.3623436951405168</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2778944475244032</v>
+        <v>-0.2792812598796317</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1210879426386313</v>
+        <v>-0.1081088002401671</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.0839852660810223</v>
+        <v>0.09709607045596158</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1496402417688998</v>
+        <v>-0.1365973454745344</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1136671950192039</v>
+        <v>-0.115094215627586</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2475398410624479</v>
+        <v>-0.2489444849038662</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.00162636448644804</v>
+        <v>-0.003098692859595076</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1198651164670892</v>
+        <v>0.1183370753481299</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.01676975156539839</v>
+        <v>-0.01826770308232284</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1389595846482621</v>
+        <v>0.1374203874009794</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.02687018492301974</v>
+        <v>-0.02837727781736987</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1048728087595379</v>
+        <v>0.106010232059468</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1051088598433267</v>
+        <v>-0.092586570167704</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2052185447444828</v>
+        <v>-0.206225542136778</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.09533401099272965</v>
+        <v>-0.0963776405846275</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.05438202912714729</v>
+        <v>-0.05543420821616252</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.07903138112368424</v>
+        <v>0.09214218549862352</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.06639579945949947</v>
+        <v>0.07943869575386486</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.03005231362978833</v>
+        <v>-0.03111145679396543</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.06945254586833727</v>
+        <v>-0.07051115181081258</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.06481342555336767</v>
+        <v>0.06371838549770814</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08258486163571632</v>
+        <v>0.08146807725507443</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.05589259364346333</v>
+        <v>-0.05697811154794863</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.01892081983613991</v>
+        <v>0.01781607363812299</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1279030533508987</v>
+        <v>-0.1289785729145052</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.006990824419006003</v>
+        <v>0.007842176750401109</v>
       </c>
     </row>
     <row r="30">
@@ -5156,101 +5156,101 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3932</v>
+        <v>3933</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1607811193986137</v>
+        <v>-0.148258829722991</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2373984409094589</v>
+        <v>-0.2381467483446329</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1619810963918269</v>
+        <v>-0.1627548170014563</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.06868865915520672</v>
+        <v>-0.06948448855988687</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.04118985644470996</v>
+        <v>0.0403576923906499</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.05944397690148406</v>
+        <v>0.07248687319584945</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.01397658376259869</v>
+        <v>0.0131572245895768</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.08380373805456287</v>
+        <v>-0.0846056483233113</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.02158670346506852</v>
+        <v>0.02075671959347147</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.07472501195600501</v>
+        <v>0.07386842409352568</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1411723088078958</v>
+        <v>-0.1419775227164024</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.009158288798666092</v>
+        <v>0.008314979697289004</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.06625696861775054</v>
+        <v>-0.06708781011085563</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.04526446965575559</v>
+        <v>0.04590531021312216</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.009675</t>
+          <t>X &lt; 0.009674</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.07912758716018686</v>
+        <v>-0.07971543023420935</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1260329541952601</v>
+        <v>-0.126628018018998</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.03179553338784302</v>
+        <v>-0.03241905389876365</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1621701893814915</v>
+        <v>0.1614993198408996</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1382823571534431</v>
+        <v>0.1376109053742951</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1990124539571241</v>
+        <v>0.1983289241962751</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1280120414301393</v>
+        <v>0.1273449909853213</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.07557133752163026</v>
+        <v>0.07491168151040739</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2039016331488313</v>
+        <v>0.2032087867853249</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1700822217968962</v>
+        <v>0.1693876424571101</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.029598707159181</v>
+        <v>0.02893664254360573</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2035473439334297</v>
+        <v>0.2028417278422339</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1487751837997422</v>
+        <v>0.1480780818990795</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1868532050653613</v>
+        <v>0.1873140572912959</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4023</v>
+        <v>4024</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.164399668079156</v>
+        <v>-0.1648397362564253</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07775047096853172</v>
+        <v>-0.07822699971314506</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1357167821429073</v>
+        <v>0.1351834928859361</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1803352996802232</v>
+        <v>0.1797918930437703</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2258798491930776</v>
+        <v>0.2253199546908959</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.264114128405005</v>
+        <v>0.2635472228856486</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1681830714088832</v>
+        <v>0.1676389254183164</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.136557757406031</v>
+        <v>0.1360169102104578</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2878962728270054</v>
+        <v>0.2873170470114559</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2213597195496675</v>
+        <v>0.2207889264747465</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.08026635764920087</v>
+        <v>0.07972845179305921</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2280305506850056</v>
+        <v>0.2274560014295943</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1697222741559656</v>
+        <v>0.1691580730482229</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2844284426300803</v>
+        <v>0.2847594975730701</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1815839178489256</v>
+        <v>-0.181924144623359</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01552927223782063</v>
+        <v>0.0151285699581365</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1014973129850816</v>
+        <v>0.1010723711055803</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2451891307889369</v>
+        <v>0.2447295879910456</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2864367528999097</v>
+        <v>0.285962894347179</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2527273696293904</v>
+        <v>0.252263782872518</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2061373307202032</v>
+        <v>0.2056843833874638</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1959387749622366</v>
+        <v>0.1954846949285312</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3703648283254068</v>
+        <v>0.3698671177568684</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3227030124409609</v>
+        <v>0.3222105669089075</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1811637788492746</v>
+        <v>0.1807044923093244</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.3281140301712639</v>
+        <v>0.3276185543033705</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2424850070825357</v>
+        <v>0.2420073274768555</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.3335354187461306</v>
+        <v>0.3337747303010232</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1334481025528476</v>
+        <v>-0.1337277664756797</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.02903894745199409</v>
+        <v>0.02870981086012137</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.08783651217436983</v>
+        <v>0.08749048381899627</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1825017145694261</v>
+        <v>0.1821331375595818</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2449500537742964</v>
+        <v>0.2445628163538345</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.286552862884669</v>
+        <v>0.2861570420070976</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2642480360477109</v>
+        <v>0.2638569963869131</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3004844286767536</v>
+        <v>0.3000815515332818</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.4000978746015988</v>
+        <v>0.3996700526398058</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3479196556671411</v>
+        <v>0.3474993560650148</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2305459755337864</v>
+        <v>0.2301530368244826</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3278298068055676</v>
+        <v>0.3274130469977052</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2893686344050721</v>
+        <v>0.288958608568322</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3077243244792314</v>
+        <v>0.3079097791068293</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.162464436880704</v>
+        <v>-0.1627120285821775</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.0278634956742323</v>
+        <v>-0.02815289245344132</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.03003389014370583</v>
+        <v>0.02972805414677993</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1247545153085881</v>
+        <v>0.1244261163096212</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1860143122135653</v>
+        <v>0.1856678466729136</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2525408205632544</v>
+        <v>0.252179576226041</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2301055994056398</v>
+        <v>0.229749212918918</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2653489600620844</v>
+        <v>0.2649812348521579</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.3646395783700314</v>
+        <v>0.3642470793382131</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.3353529851633184</v>
+        <v>0.3349628078621478</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2178051910529746</v>
+        <v>0.2174424731469671</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3394365636424439</v>
+        <v>0.3390441115496401</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.275750730103276</v>
+        <v>0.2753713813301033</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.3190420977565935</v>
+        <v>0.319203993388868</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_10.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_10.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.750498711038361</v>
+        <v>-2.501675578417938</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.425266860328556</v>
+        <v>5.890209724177666</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.032813999794037</v>
+        <v>5.498405806058337</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.722615566569623</v>
+        <v>8.123554951949053</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.629353164311169</v>
+        <v>5.142767113959941</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.368462884183067</v>
+        <v>2.920935047331618</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.404374520754729</v>
+        <v>7.852536708952115</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.50048088983115</v>
+        <v>12.38179735307336</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.198628309897863</v>
+        <v>2.360197760323338</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.91139874176087</v>
+        <v>4.035282743449088</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.707476989481314</v>
+        <v>3.832197049748203</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.868178726963855</v>
+        <v>8.888815798459994</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.323104913472562</v>
+        <v>3.497146408934441</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.01472564286518008</v>
+        <v>1.247016706443901</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15.32717865130133</v>
+        <v>14.11152710058106</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.042400442787965</v>
+        <v>5.151395065442976</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.648898308166444</v>
+        <v>4.759440347335016</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.7827627044248757</v>
+        <v>1.195983792391608</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.320109930328037</v>
+        <v>0.7080486874698195</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>13.23345726657199</v>
+        <v>15.76571000509806</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.586941255785376</v>
+        <v>12.01175760875314</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.556694821242438</v>
+        <v>4.153009835163914</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.064276442898475</v>
+        <v>7.816344160809443</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.217426499839576</v>
+        <v>6.995243514177176</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.014837313577658</v>
+        <v>6.792909464642918</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.62082588982511</v>
+        <v>10.55458383711993</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.633129721899465</v>
+        <v>6.459360422234219</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.7178750897327646</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.98140316999077</v>
+        <v>-11.01060011563836</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.000104297658126</v>
+        <v>1.998934096818751</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.606362765372161</v>
+        <v>1.606221389565476</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.602890195137377</v>
+        <v>6.60243976691477</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.067412179842258</v>
+        <v>6.115879645840835</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.93115876210144</v>
+        <v>3.95508781734631</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.847627970074363</v>
+        <v>3.89557032741844</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.817482318645965</v>
+        <v>5.866677161886479</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.194097513430876</v>
+        <v>8.267287116120507</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.78365590294014</v>
+        <v>9.88292637699719</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1672468623495362</v>
+        <v>-0.06741733308720654</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1329448819689674</v>
+        <v>-0.009312892897320069</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5529976103415422</v>
+        <v>-0.4043473199952459</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3274210775118931</v>
+        <v>-0.1554223179452308</v>
       </c>
     </row>
     <row r="9">
@@ -731,254 +731,254 @@
         <v>69</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.916949078997568</v>
+        <v>6.887915822579096</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.911682722685491</v>
+        <v>-1.912885649448874</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.029228933233647</v>
+        <v>2.029091565930614</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.942241452691377</v>
+        <v>7.941803119731595</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.623402742132456</v>
+        <v>1.67184039576096</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.418736113933718</v>
+        <v>-2.39484364407695</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.057171638154017</v>
+        <v>-1.009255311438409</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.264299775651253</v>
+        <v>4.313487151361805</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.032547348401252</v>
+        <v>-2.95939909750485</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.882376523928563</v>
+        <v>-3.783146655879548</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.19155389349217</v>
+        <v>-1.091728782301224</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.157516027162551</v>
+        <v>-1.033887327101091</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.373446535321015</v>
+        <v>-7.224802256546624</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.352518285008131</v>
+        <v>-1.180519525440808</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.008688</t>
+          <t>X ≈ -0.008687</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.924525314910575</v>
+        <v>1.895451984077049</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3194288439286979</v>
+        <v>0.318244537363789</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.324243852458771</v>
+        <v>4.324126351569461</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.8120806003068</v>
+        <v>-5.812616959824894</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4817589572004266</v>
+        <v>-0.4333388611976332</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.58795460895346</v>
+        <v>-4.564077826239703</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.197950291074747</v>
+        <v>1.245874758123911</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7366485440738586</v>
+        <v>-0.6874849149798266</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.608559624831372</v>
+        <v>3.681728282802602</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.229519265264756</v>
+        <v>4.32876866776791</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.556616576790425</v>
+        <v>2.656447003551079</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3480275182992187</v>
+        <v>-0.2244000894203495</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.172302787556312</v>
+        <v>2.320952360623139</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.398547358643285</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.007793</t>
+          <t>X ≈ -0.007791</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>73</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.78972660429104</v>
+        <v>-1.818831886250791</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.431986728328674</v>
+        <v>3.430831317146662</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.059371939440148</v>
+        <v>-1.059532395349919</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4370064482567528</v>
+        <v>0.4365150559543522</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.09986259412446685</v>
+        <v>-0.05144468636652277</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.56372427451489</v>
+        <v>1.58763496720124</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.112056085968895</v>
+        <v>0.1599716713926114</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.013217957139268</v>
+        <v>1.062386459728195</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.32081218235512</v>
+        <v>2.393973079016391</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.209232770499796</v>
+        <v>4.308478933668603</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.206805651222048</v>
+        <v>-4.10699357468679</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.435275686045024</v>
+        <v>-1.311652538270302</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.594654774295115</v>
+        <v>-4.44601186623472</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.370187532575436</v>
+        <v>-4.198188773008148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.006897</t>
+          <t>X ≈ -0.006896</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>87</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.263746536896697</v>
+        <v>7.234739336799443</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.805837056869727</v>
+        <v>6.804716994492964</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.7052971151344</v>
+        <v>8.705222714283117</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.399079308550327</v>
+        <v>5.398628238563631</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.863616976542708</v>
+        <v>4.912065365691518</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.455363735678262</v>
+        <v>7.47931089574535</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.372681812220975</v>
+        <v>7.420634346454605</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>12.64588080299908</v>
+        <v>12.69510255185387</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>13.73643729925797</v>
+        <v>13.8096405949831</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.446613264441325</v>
+        <v>9.545872576505602</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>11.54179867353696</v>
+        <v>11.64164439129543</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>12.72805704899209</v>
+        <v>12.85169984145148</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>15.75886810819061</v>
+        <v>15.90752530941355</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>17.13823633768184</v>
+        <v>17.3102350972485</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.006001</t>
+          <t>X ≈ -0.006</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>118</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-5.849804073836097</v>
+        <v>-5.878942808071386</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9893943855760838</v>
+        <v>0.9882218291073031</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.129734122430229</v>
+        <v>3.129616025131185</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9641688841403493</v>
+        <v>-0.9646697718960695</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1893927176874755</v>
+        <v>0.2378013000495969</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.022549637533274</v>
+        <v>3.046468464299842</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.630333152808475</v>
+        <v>4.678268218542534</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.010940018269189</v>
+        <v>5.060124452829122</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.183012007811939</v>
+        <v>9.25619588848442</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.87632128107816</v>
+        <v>10.97558232417425</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>12.36854020349138</v>
+        <v>12.46838614557788</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>9.865445303525753</v>
+        <v>9.98908128444932</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>11.14273897386829</v>
+        <v>11.29139107636555</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>15.60891625196199</v>
+        <v>15.78091501152866</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>147</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.35532868268978</v>
+        <v>7.326349936114298</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.717937882135885</v>
+        <v>3.716797905905757</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.968126505134194</v>
+        <v>1.968001764438483</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.491248616834511</v>
+        <v>5.490807094178116</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.8850941928905129</v>
+        <v>0.9334981546261787</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.253606495207009</v>
+        <v>5.277540827670208</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.812645210544773</v>
+        <v>3.860571335684007</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.026137637511177</v>
+        <v>4.075313942321358</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.325055448910319</v>
+        <v>5.398218908341363</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.157380378858612</v>
+        <v>5.256616405898818</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.954653936988528</v>
+        <v>5.054476821633038</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.310780197854228</v>
+        <v>4.434402467291079</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.212151955540804</v>
+        <v>3.36079449390018</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.11923563395208</v>
+        <v>4.291234393518742</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>192</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.678035566122972</v>
+        <v>2.145539206896984</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.001938315478064</v>
+        <v>-1.525822431453584</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.397024871875843</v>
+        <v>-2.158941658652495</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.925243232909224</v>
+        <v>2.924785972870744</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.986920640731874</v>
+        <v>5.035349428181945</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.244987422780319</v>
+        <v>4.268915406953361</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.201169323036893</v>
+        <v>5.24909976280351</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.656651883811058</v>
+        <v>2.705815003067492</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.716800519240159</v>
+        <v>5.789959397689117</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.870025082462924</v>
+        <v>4.969250698878902</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.62671910150258</v>
+        <v>3.726530616294212</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>7.306068543448063</v>
+        <v>7.429690368442408</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>7.929962748976436</v>
+        <v>8.078605723312627</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>9.200017946877246</v>
+        <v>9.372016706443908</v>
       </c>
     </row>
     <row r="16">
@@ -1095,774 +1095,774 @@
         <v>248</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.274582075284052</v>
+        <v>-3.114390283279697</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3417688349634034</v>
+        <v>0.3407661037913527</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8560600244349459</v>
+        <v>-0.8564230633994256</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.530311857320534</v>
+        <v>-1.530813328979441</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3449987228244211</v>
+        <v>0.3933663171301589</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.174280409824995</v>
+        <v>-2.15041385880253</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.455028352601019</v>
+        <v>-1.407160681469847</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7145273455857151</v>
+        <v>-0.665398103627787</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.178387235312222</v>
+        <v>-1.105279783735597</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3890932982393736</v>
+        <v>0.4882827740718128</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6202868719393848</v>
+        <v>-0.5205030574175851</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.391785270193566</v>
+        <v>-1.268193246131602</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.617959358676217</v>
+        <v>-2.469334856749164</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.795949795058242</v>
+        <v>-2.623951035491579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002418</t>
+          <t>X ≈ -0.002419</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.73598208267515</v>
+        <v>3.680180473649088</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.374080233434285</v>
+        <v>-3.351451411892882</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.037817737765863</v>
+        <v>-3.017330863965263</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.374330992832107</v>
+        <v>-4.342305537925206</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.082944617800287</v>
+        <v>-3.012866834212147</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-5.351747618177107</v>
+        <v>-5.289696595675743</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.33667374888207</v>
+        <v>-4.260389757449168</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-7.37586802577438</v>
+        <v>-7.276188765331938</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5.40226776157089</v>
+        <v>-5.494499579836464</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.217904512275503</v>
+        <v>-4.496592207718635</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.25928635858947</v>
+        <v>-6.524107453117544</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.492153059030478</v>
+        <v>-5.738648916660331</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-6.281118901097052</v>
+        <v>-6.500022906384437</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.057334994299225</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001522</t>
+          <t>X ≈ -0.001523</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.351542287796725</v>
+        <v>-1.566831087337306</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6909424711625363</v>
+        <v>-0.8858628150341445</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.997952574638852</v>
+        <v>-2.789214546614318</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.839781934722382</v>
+        <v>-7.565539489492423</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.854717517912178</v>
+        <v>-6.547832455555252</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-8.470266300785269</v>
+        <v>-8.165949128240726</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-7.790197297766312</v>
+        <v>-7.644022860395424</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-7.882425337013572</v>
+        <v>-7.733793177854778</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.087041160552431</v>
+        <v>-8.908785953307941</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-10.32731259545643</v>
+        <v>-10.11295777387269</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-9.178058348292211</v>
+        <v>-9.184891099854937</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.631950491740369</v>
+        <v>-6.859556431109674</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.307742394638225</v>
+        <v>-5.742315973510493</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.850269409444586</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0006264</t>
+          <t>X ≈ -0.0006274</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1918306059209414</v>
+        <v>0.5768070048254614</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.63944945468144</v>
+        <v>1.051110912849175</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.395958129856112</v>
+        <v>-1.401420708538538</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7877206768327127</v>
+        <v>1.198556268401006</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.892877943084194</v>
+        <v>1.945045827159397</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.834484039670102</v>
+        <v>3.681528963401632</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.395441845542969</v>
+        <v>5.267377528622298</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.108210125586929</v>
+        <v>3.980855752468848</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3450217066860262</v>
+        <v>0.23397803589706</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.09320799696136817</v>
+        <v>-0.1758353865307569</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.347730853360105</v>
+        <v>1.27160509274357</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.2634751847589314</v>
+        <v>-0.3216625419082391</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.784703732549772</v>
+        <v>1.761659499192263</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.103994398801767</v>
+        <v>-2.120751888597418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002692</t>
+          <t>X ≈ 0.0002679</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3420361955311293</v>
+        <v>0.5024031705740981</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7470367224397094</v>
+        <v>0.9271030262084992</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.563186392391124</v>
+        <v>2.140275640365992</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.905306084811031</v>
+        <v>3.073573830800434</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.984787060899713</v>
+        <v>4.413517109805163</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.880530270790935</v>
+        <v>4.283547409683379</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.371673107060737</v>
+        <v>1.810062394624055</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4980623350741453</v>
+        <v>0.9451441999236465</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.182168993329242</v>
+        <v>-0.7002671381044649</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.440258566251018</v>
+        <v>-1.925143350812895</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.647168042509087</v>
+        <v>-2.129286576568518</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.206275352060146</v>
+        <v>-1.669904524072095</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.413875598086058</v>
+        <v>-0.8564988476131035</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.578828206968907</v>
+        <v>-2.220725229039964</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.001165</t>
+          <t>X ≈ 0.001163</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.151816912123586</v>
+        <v>1.10254340158933</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.740498406571717</v>
+        <v>-3.143635877507243</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8436721829289269</v>
+        <v>-0.8751499968679113</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7134470422368722</v>
+        <v>-0.745350863833572</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4878691648098297</v>
+        <v>-0.4738756622287639</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.487332444181391</v>
+        <v>-2.483022597902419</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.573713115508092</v>
+        <v>-2.543579627584194</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.658921435339586</v>
+        <v>-2.800860682651283</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.03791125469778933</v>
+        <v>-0.1750712743919323</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.270971813479669</v>
+        <v>-1.377489376303032</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.05689407806865887</v>
+        <v>-0.05728933296951766</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2918695320282225</v>
+        <v>-0.3812715710188286</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4374049020146131</v>
+        <v>0.3679575681520575</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.812565839597553</v>
+        <v>1.762283882016426</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.00206</t>
+          <t>X ≈ 0.002059</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.2063378085127</v>
+        <v>-1.237426264313392</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.080276837476475</v>
+        <v>-1.729971127242223</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.650624665644671</v>
+        <v>-4.66951000259256</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.259572155835265</v>
+        <v>-1.266510322358819</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.07422010021785</v>
+        <v>-1.028343130299184</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.59334507300936</v>
+        <v>-2.573989049055754</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5001539408349203</v>
+        <v>-0.452482092424134</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.5547395230308894</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.028506865982962</v>
+        <v>-1.118924000235985</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6670288831417182</v>
+        <v>0.6073445202722354</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.8259640885178925</v>
+        <v>0.7687350633202144</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5942032136722375</v>
+        <v>-0.6315041908176013</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4401913875598069</v>
+        <v>0.4318984624423834</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.152254780395481</v>
+        <v>-1.508457746110793</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.002956</t>
+          <t>X ≈ 0.002955</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>276</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.577052545764914</v>
+        <v>-1.968741837749889</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.585585049435004</v>
+        <v>2.224545774272464</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.3866503762008264</v>
+        <v>0.3864991977394752</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.32301575866493</v>
+        <v>1.960645462371531</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.424743090559431</v>
+        <v>1.110411903966835</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9981710372865393</v>
+        <v>1.383141785024755</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1702924120156268</v>
+        <v>0.2394304408788983</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2854397174173258</v>
+        <v>0.4955943342816838</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.398370604372765</v>
+        <v>2.625001150830755</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.910770648622659</v>
+        <v>2.003613512263044</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.256794128043623</v>
+        <v>0.3569889520959961</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.222833603745009</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.682615629984085</v>
+        <v>2.191526265063374</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.99530780194975</v>
+        <v>3.167306561516291</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.003852</t>
+          <t>X ≈ 0.00385</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.713978739964773</v>
+        <v>3.455021832671157</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.685476921095471</v>
+        <v>4.863524923550976</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.154629088586702</v>
+        <v>4.899827877143565</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.719577539483076</v>
+        <v>2.899632517346618</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.607930014355567</v>
+        <v>5.811599463010417</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.912006328868614</v>
+        <v>5.661179050364439</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.257639915598546</v>
+        <v>3.469304391720307</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.6446485250305898</v>
+        <v>0.8802272407677378</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.442035467220336</v>
+        <v>1.69080566296779</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.738039417671487</v>
+        <v>2.998955097176172</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.533338259411352</v>
+        <v>2.801727268550806</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.007390884370636286</v>
+        <v>0.3019395127795832</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8567262870403241</v>
+        <v>-0.9463028369234934</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.206097932951145</v>
+        <v>-2.83417987475265</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.004748</t>
+          <t>X ≈ 0.004745</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>215</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-8.237831514516948</v>
+        <v>-7.823444328598875</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-7.06456688046547</v>
+        <v>-7.076867766402529</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.612384834328047</v>
+        <v>-5.151442094220862</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.713948417898884</v>
+        <v>-2.248030354540653</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.261418691666741</v>
+        <v>-2.746623601541955</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.965808069910878</v>
+        <v>-2.46947749989998</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.659018433538151</v>
+        <v>-1.608323764717845</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2656219610457882</v>
+        <v>-0.6768026890124688</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.117301791987195</v>
+        <v>-3.495401221857627</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.641639192968192</v>
+        <v>-2.002557903789402</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.01412476505063864</v>
+        <v>-0.3500051053627686</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5136191964757444</v>
+        <v>0.1701989631596632</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.627461889395803</v>
+        <v>-3.939315362395909</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.006377401959938</v>
+        <v>-2.299494921463044</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.005644</t>
+          <t>X ≈ 0.005641</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-9.224637136186324</v>
+        <v>-9.279658388472491</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.999319958059218</v>
+        <v>-2.071673253386798</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.685969708892408</v>
+        <v>0.9163494047114469</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.598477627606599</v>
+        <v>-1.658562980206469</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.562119038365239</v>
+        <v>-6.204432925046895</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.955557581747982</v>
+        <v>-5.932986355285678</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-10.16172630228616</v>
+        <v>-10.05179347589411</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.889068918675711</v>
+        <v>-7.137204538922106</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.580188061499818</v>
+        <v>-5.820057429061286</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-4.005449323583065</v>
+        <v>-3.261360249715985</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.210150481843215</v>
+        <v>-3.763676422154859</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.175772329487934</v>
+        <v>-3.715106781077019</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.85619715540404</v>
+        <v>-1.397026389083457</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.630461505177507</v>
+        <v>-1.15094247722957</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.006539</t>
+          <t>X ≈ 0.006536</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>136</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>7.351957663731177</v>
+        <v>7.748325399378921</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6586249380516165</v>
+        <v>1.068128174776717</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.907314058815459</v>
+        <v>4.325712294396354</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.913633685259946</v>
+        <v>5.91040100586266</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.180609110531996</v>
+        <v>3.219430633662611</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.754167153675567</v>
+        <v>2.771318559312583</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.935372811331916</v>
+        <v>1.979357289787188</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.46830416754522</v>
+        <v>1.523932116534887</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.142616128669459</v>
+        <v>2.207857100566983</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1778909029545162</v>
+        <v>-0.07988278923932768</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3527020564323067</v>
+        <v>0.4563885822642035</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.122374326434731</v>
+        <v>1.240332866277328</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.7683647621728582</v>
+        <v>-0.61657538044836</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.398547358641935</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.007435</t>
+          <t>X ≈ 0.007432</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.242983300921452</v>
+        <v>1.696923034139949</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.357264934464517</v>
+        <v>4.78838481366838</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.476421671043603</v>
+        <v>5.334759008279242</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.834617995992993</v>
+        <v>0.7822976294210378</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.08851860901405217</v>
+        <v>-1.577367534160224</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.883514279744887</v>
+        <v>6.18829161028652</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.010033444816031</v>
+        <v>1.441086525321587</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.389118647183139</v>
+        <v>4.718888193974472</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.481982644506516</v>
+        <v>0.9382811558014481</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.25255153643873</v>
+        <v>-2.696776226512796</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.457252694698923</v>
+        <v>-2.905820845659846</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.307489926959008</v>
+        <v>-5.672278564337219</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.7661023187339</v>
+        <v>-5.158540999399584</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.540366668507424</v>
+        <v>-4.366190840725906</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.008331</t>
+          <t>X ≈ 0.008327</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.210644815252166</v>
+        <v>-3.178750461946187</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.036255619288724</v>
+        <v>-1.936205499877452</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.837327153562732</v>
+        <v>-3.740105092179647</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8587658976237904</v>
+        <v>-0.8195914588625257</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.806604310539647</v>
+        <v>-2.716302784177138</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3100039790929117</v>
+        <v>-1.046852759494548</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>1.699317261131114</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.863628605564088</v>
+        <v>-1.54904683248045</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.353182190658288</v>
+        <v>-2.993481625979939</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3459581298452932</v>
+        <v>-1.018582355818111</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.836373573819778</v>
+        <v>-5.393820383571644</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5162811357501269</v>
+        <v>-1.166050745190574</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.349282296650756</v>
+        <v>2.652901421893326</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.146446518305851</v>
+        <v>1.493495579683298</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.009227</t>
+          <t>X ≈ 0.009223</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.017467938437903</v>
+        <v>3.912087590917928</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.225327282438826</v>
+        <v>5.944604829595598</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>9.786089815243052</v>
+        <v>7.500815526841805</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>17.6329653970008</v>
+        <v>15.22523655392527</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.503633974382197</v>
+        <v>5.349392323370445</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.732199175714783</v>
+        <v>7.524759353202235</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.779264214046854</v>
+        <v>5.529943636598588</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>12.15834941641393</v>
+        <v>10.62975388560974</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>14.02044418296808</v>
+        <v>12.52694090385115</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.401294617407451</v>
+        <v>6.042734964545602</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.96582422837803</v>
+        <v>13.22787374650345</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>14.92327930381028</v>
+        <v>14.48929276449167</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>16.42620537357374</v>
+        <v>15.19608505197571</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.88271025456955</v>
+        <v>9.784752555500567</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>39</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-8.891172440790804</v>
+        <v>-8.920368235143435</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.882256850760825</v>
+        <v>4.88107006431617</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>17.30799828651858</v>
+        <v>17.30784489651425</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.053608045491551</v>
+        <v>2.053113553113548</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.207626184703592</v>
+        <v>9.256172104469364</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.940897650236074</v>
+        <v>6.964855059185687</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.292084726867344</v>
+        <v>4.340096405857665</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.389118647183203</v>
+        <v>6.43836620957692</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.892239054762953</v>
+        <v>8.96549616454265</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.478217694330567</v>
+        <v>5.577565019625141</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.273516536070339</v>
+        <v>5.373424572089014</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.743792124323129</v>
+        <v>2.867488745351373</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.323641271009691</v>
+        <v>2.472330818787519</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>30</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.57456454306843</v>
+        <v>12.57337775662378</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.97668496856847</v>
+        <v>8.976190476190467</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.438395415472776</v>
+        <v>8.486941335238548</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.26423055489213</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.317725752508295</v>
+        <v>5.365737431498616</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.183990442054913</v>
+        <v>8.23323800444863</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.93975615586895</v>
+        <v>14.03910348116352</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.7350549976088</v>
+        <v>13.83496303362747</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.76943314996408</v>
+        <v>13.89312977099232</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.01594896331736</v>
+        <v>10.16463851109518</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.908351280210574</v>
+        <v>7.080350039777237</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>23</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.388649186856959</v>
+        <v>8.359453392504328</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.4296370068366</v>
+        <v>2.428450220391944</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.312960464874962</v>
+        <v>-2.313113854879283</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-10.87838749519964</v>
+        <v>-10.87888198757764</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-7.068850961338811</v>
+        <v>-7.020305041573039</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.272001329165846</v>
+        <v>6.295958738115459</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.53511705685622</v>
+        <v>10.58312873584654</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>18.76370058698249</v>
+        <v>18.8129481493762</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.659240169590163</v>
+        <v>5.732497279369859</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.809321373260303</v>
+        <v>4.908668698554877</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.952446301956627</v>
+        <v>9.052354337975302</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2911722803989036</v>
+        <v>0.4148689014271483</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.56667360099857</v>
+        <v>8.715363148776397</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.251069009644496</v>
+        <v>-4.079070250077834</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>8</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.98091603053427</v>
+        <v>-15.0101118248869</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-29.09210212359818</v>
+        <v>-29.09328891004284</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-29.48687350835322</v>
+        <v>-29.48702689835754</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-29.35664836476486</v>
+        <v>-29.35714285714286</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-29.89493791786055</v>
+        <v>-29.84639199809478</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-17.09756388822547</v>
+        <v>-17.07360647927585</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-17.18227424749163</v>
+        <v>-17.13426256850131</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-17.64934289127829</v>
+        <v>-17.60009532888457</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-17.71032504780106</v>
+        <v>-17.63706793802137</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.264945002391286</v>
+        <v>-6.165036966372611</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>6.393129770992367</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.075017946877331</v>
+        <v>6.247016706443993</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4085</v>
+        <v>4096</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1301137400854557</v>
+        <v>0.1304333199171026</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.3135605564115806</v>
+        <v>0.3127480909308673</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1273843041467799</v>
+        <v>0.1270466346349082</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2953662872497915</v>
+        <v>0.2945863196715592</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2589458144306036</v>
+        <v>0.2571402796153279</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1544517482270109</v>
+        <v>0.1534890372933475</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2053112852551848</v>
+        <v>0.2036609021299327</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1427617286189573</v>
+        <v>0.1412503561470402</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1441981795827161</v>
+        <v>0.1421322570529213</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1637718076175858</v>
+        <v>0.1610547006757628</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.09513327549529293</v>
+        <v>0.09258684431300424</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1433015130666391</v>
+        <v>0.1400795025687458</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1530023162297667</v>
+        <v>0.1491800455513115</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1233655600963388</v>
+        <v>0.1190870189439082</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4046</v>
+        <v>4056</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1675195447304887</v>
+        <v>0.1563910013602481</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2450097541741201</v>
+        <v>0.2577435383347435</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.06082183303204403</v>
+        <v>0.07407465069582031</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.204495619456047</v>
+        <v>0.2173775560396294</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1975405038410543</v>
+        <v>0.2089585554107529</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.113832263723225</v>
+        <v>0.1261966703304438</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.116640136914981</v>
+        <v>0.1282282018654115</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.03328297249260004</v>
+        <v>0.02053490252843915</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1340343696266402</v>
+        <v>0.1202578438056818</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1372870200665233</v>
+        <v>0.1228473235280987</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.0699525031657231</v>
+        <v>0.05570705924954211</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.06884026458863701</v>
+        <v>0.05380005191892678</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1320843722622769</v>
+        <v>0.1161626257940824</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.124696641884654</v>
+        <v>0.1079634520060395</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4018</v>
+        <v>4029</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.06187732099132148</v>
+        <v>0.06287184656279265</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2255157424067846</v>
+        <v>0.2249491498433329</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.04278645689870331</v>
+        <v>0.04267607193948919</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.211375468402963</v>
+        <v>0.2108195097796468</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2081164650547649</v>
+        <v>0.2056139454416268</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.02240630551521861</v>
+        <v>0.02138980509372601</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.05064500716675013</v>
+        <v>0.04859174269788724</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.005207702411581749</v>
+        <v>-0.007158525910675451</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07180271754809553</v>
+        <v>0.06868317749664499</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08097942787297541</v>
+        <v>0.07679254637557165</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0145874522220808</v>
+        <v>0.01055827172270796</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01166137739906503</v>
+        <v>-0.0165700553534478</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.07981227923344392</v>
+        <v>0.07365422656253884</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1205629941644517</v>
+        <v>0.1133607124007199</v>
       </c>
     </row>
     <row r="9">
@@ -2370,257 +2370,257 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3977</v>
+        <v>3988</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.175725573475674</v>
+        <v>0.1767164680397855</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2072210150330562</v>
+        <v>0.2067110899571674</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.02666711351237439</v>
+        <v>0.0266015087442355</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1454835640036336</v>
+        <v>0.145108268419925</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1477113545930422</v>
+        <v>0.144851434479655</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.01789011156297704</v>
+        <v>-0.01905192472129613</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.01150085290997538</v>
+        <v>0.009041561661391029</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.06523543458743575</v>
+        <v>-0.06754650564980835</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01193228034760807</v>
+        <v>-0.01560537854236799</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.01904816465349057</v>
+        <v>-0.02402277134144981</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.0164620327846805</v>
+        <v>0.01135992663675012</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01041103199113991</v>
+        <v>-0.01664466509785711</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.08633609252803609</v>
+        <v>0.07856848519063675</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1251813866559672</v>
+        <v>0.1161240284098</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.009136</t>
+          <t>X &gt; -0.009135</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3908</v>
+        <v>3919</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.05670192406906693</v>
+        <v>0.05855551997567687</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2446325702793715</v>
+        <v>0.2440298383672328</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.00869029835067181</v>
+        <v>-0.008655397085277627</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.007823304454134927</v>
+        <v>0.00783550885358153</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1216564145366874</v>
+        <v>0.1179664540437173</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.02449944170302842</v>
+        <v>0.022777528872858</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.03036943066928899</v>
+        <v>0.02697023842686264</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1416780982277785</v>
+        <v>-0.1446813161457996</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.04139997136572759</v>
+        <v>0.03622462059220766</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.04916310883422881</v>
+        <v>0.04216236467108558</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.03779087078701338</v>
+        <v>0.03078149359687643</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.00984235712524395</v>
+        <v>0.001265450665918877</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2180466865202462</v>
+        <v>0.207155517897931</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1512717851577037</v>
+        <v>0.1389534249945612</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.00824</t>
+          <t>X &gt; -0.008239</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3840</v>
+        <v>3851</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.02362588485625139</v>
+        <v>0.02612005917098514</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.243308052933493</v>
+        <v>0.2427193736744826</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.0854193406045809</v>
+        <v>-0.08516257935184512</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1108841027676064</v>
+        <v>0.1106116106116062</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1323418950778716</v>
+        <v>0.1277012661539203</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1061783155167362</v>
+        <v>0.1037710796772444</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.00969351959960818</v>
+        <v>0.005447125640735351</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1311421632492511</v>
+        <v>-0.135096625228968</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.02176848083105654</v>
+        <v>-0.02814677619571881</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.02486403143590366</v>
+        <v>-0.03352946306470983</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.006813334423462436</v>
+        <v>-0.01558185480013918</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.0161796361692268</v>
+        <v>0.005250196634719373</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1834400680644066</v>
+        <v>0.1698306190910515</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1114762802105744</v>
+        <v>0.09601696611672139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.007345</t>
+          <t>X &gt; -0.007344</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3767</v>
+        <v>3778</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.05876650914819237</v>
+        <v>0.061768945358331</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1815152354915313</v>
+        <v>0.1811174224109919</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.06654529236593021</v>
+        <v>-0.06633542303423923</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1045642378297984</v>
+        <v>0.1043143762256733</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1368417431563884</v>
+        <v>0.1311627946171328</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.07793280051625118</v>
+        <v>0.07509927878014366</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.007709854257178961</v>
+        <v>0.002461341670411343</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1533185074988879</v>
+        <v>-0.1582348637683779</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.06716492054770384</v>
+        <v>-0.07494792744783041</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1069158144306641</v>
+        <v>-0.1174274548491283</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.07457754402789618</v>
+        <v>0.06347400955976212</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.04430712183994956</v>
+        <v>0.03069590855850635</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2760338890073939</v>
+        <v>0.2590197406973971</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1983256187646916</v>
+        <v>0.1789912961739262</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.006449</t>
+          <t>X &gt; -0.006448</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3680</v>
+        <v>3691</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1115686165078174</v>
+        <v>-0.1073040495090183</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.02490762721438955</v>
+        <v>0.02499356362716298</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2739230884128219</v>
+        <v>-0.2730884866881667</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.02060500433125156</v>
+        <v>-0.02047709113367802</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.02509461128013157</v>
+        <v>0.01847286677007531</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.09647928952698948</v>
+        <v>-0.09942426786737002</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1664076893142479</v>
+        <v>-0.1723912867273825</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4559082738068554</v>
+        <v>-0.4611989263961576</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3935000817224577</v>
+        <v>-0.4022194531729681</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3327737029800844</v>
+        <v>-0.345199631150372</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.196522520718645</v>
+        <v>-0.2094332847266074</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2555532704595649</v>
+        <v>-0.2715060264622764</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.09000050693526163</v>
+        <v>-0.1098288056256322</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2021559661662309</v>
+        <v>-0.2248066476606709</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3562</v>
+        <v>3573</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.07852452890620754</v>
+        <v>0.08330702620057195</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.007043365903719234</v>
+        <v>-0.006817501395694592</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3866775945552874</v>
+        <v>-0.3854643983575414</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.01065286703805413</v>
+        <v>0.01070531478011105</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.01965183290953831</v>
+        <v>0.01122944244122692</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1998047845840105</v>
+        <v>-0.2033188501219811</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.3253115128320729</v>
+        <v>-0.3325865908476828</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6370110527133548</v>
+        <v>-0.6435432193568573</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7107455692477416</v>
+        <v>-0.7211931476357663</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7041025093020608</v>
+        <v>-0.7190737623365777</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.6127710893477243</v>
+        <v>-0.6281242146946795</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.590836210305234</v>
+        <v>-0.6103667325041329</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.462112595294272</v>
+        <v>-0.4863594370487974</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.7259365730553782</v>
+        <v>-0.7534031088373681</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3415</v>
+        <v>3426</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2347083292508074</v>
+        <v>-0.2274715224734862</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1673866289964892</v>
+        <v>-0.1665873393622164</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4880410506766282</v>
+        <v>-0.4864449955353081</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2252615034509873</v>
+        <v>-0.2244304007982691</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.01760146926241646</v>
+        <v>-0.0283425075562036</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4345489890142531</v>
+        <v>-0.4384870849834783</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5034314654928096</v>
+        <v>-0.5125031743853796</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8377380973584607</v>
+        <v>-0.846016074805398</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9705589659298042</v>
+        <v>-0.9837598645734857</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9564123144439662</v>
+        <v>-0.9754737783116525</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.8524230597346758</v>
+        <v>-0.8719486024180227</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8018281903929179</v>
+        <v>-0.8268235545618978</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6202727384780928</v>
+        <v>-0.6514299647339925</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.934498890604452</v>
+        <v>-0.9698542801293542</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3223</v>
+        <v>3234</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3486539786184082</v>
+        <v>-0.3683552763507763</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.05809903240807301</v>
+        <v>-0.08589063630670779</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3743193957991053</v>
+        <v>-0.3871502029198126</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4129428281115963</v>
+        <v>-0.411396864541139</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3157299970684662</v>
+        <v>-0.3289698581009475</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.7133175248704617</v>
+        <v>-0.7179618154880671</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.8432649595659356</v>
+        <v>-0.8545649443112566</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.045905294499178</v>
+        <v>-1.056885452341447</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.368937191543402</v>
+        <v>-1.385910173279242</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.303503837933306</v>
+        <v>-1.328407327977878</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.119253743866715</v>
+        <v>-1.14495664508739</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.284830415927352</v>
+        <v>-1.317006199341378</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.129625891934893</v>
+        <v>-1.169725218940854</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.538230579340564</v>
+        <v>-1.583842910129995</v>
       </c>
     </row>
     <row r="17">
@@ -2786,777 +2786,777 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2975</v>
+        <v>2986</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1047446784593902</v>
+        <v>-0.1402853896399918</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.09143255546962337</v>
+        <v>-0.121326293220406</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3341608492775308</v>
+        <v>-0.3481750959543319</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3197974434918294</v>
+        <v>-0.3184245660881189</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3708092315334781</v>
+        <v>-0.3889629496807601</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5915296944608031</v>
+        <v>-0.5989905808122558</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7922675405835236</v>
+        <v>-0.8086695180502659</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.073529405870786</v>
+        <v>-1.089400141718876</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.384821692096452</v>
+        <v>-1.409217720702834</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.444601010965521</v>
+        <v>-1.479291167665863</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.160848293190398</v>
+        <v>-1.19682017145783</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.275914515470873</v>
+        <v>-1.321060322715795</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.00555641302671</v>
+        <v>-1.061787111045177</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.433385414467296</v>
+        <v>-1.497457506550063</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.00197</t>
+          <t>X &gt; -0.001971</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2703</v>
+        <v>2712</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4912329059949343</v>
+        <v>-0.5262764097510555</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2388967706148648</v>
+        <v>0.205021156085003</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.06209474729127606</v>
+        <v>-0.0785037536110309</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.08820593254240805</v>
+        <v>0.08811798047653951</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.09788994738084256</v>
+        <v>-0.1238635159191119</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1125140543384191</v>
+        <v>-0.1250770675111497</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.435597733459133</v>
+        <v>-0.4599337711493448</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.4393318088993539</v>
+        <v>-0.4643337394806792</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9805503895078331</v>
+        <v>-0.9964716921620465</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.165526444795951</v>
+        <v>-1.174445856097108</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6477979218294863</v>
+        <v>-0.6585912941809937</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8516389387604661</v>
+        <v>-0.8747405311447025</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.4746822003907099</v>
+        <v>-0.5123488337874562</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9680823120942676</v>
+        <v>-1.01699509296612</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001074</t>
+          <t>X &gt; -0.001075</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2442</v>
+        <v>2448</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3992833774731253</v>
+        <v>-0.4140597288348928</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3382776232372606</v>
+        <v>0.3226655059115799</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2516885831500559</v>
+        <v>0.213827802497164</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.935546159141964</v>
+        <v>0.9135124135124073</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6242771271108296</v>
+        <v>0.56891744815929</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7807592201589841</v>
+        <v>0.7420758017832085</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3504589767309483</v>
+        <v>0.3148209345536728</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3561831013536363</v>
+        <v>0.3196275725008348</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1141318427254205</v>
+        <v>-0.1431828992933646</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1863183426983426</v>
+        <v>-0.2104886884938608</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2639129591315168</v>
+        <v>0.2609116260387339</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.2338415123363262</v>
+        <v>-0.2293192085994633</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.04187337319594064</v>
+        <v>0.05166723030032472</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.4462760744167795</v>
+        <v>-0.4523296987848511</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0001787</t>
+          <t>X &gt; -0.0001798</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2199</v>
+        <v>2206</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4646042951469553</v>
+        <v>-0.5227586180215766</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3049966977980105</v>
+        <v>0.2427544503907697</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4337614122817044</v>
+        <v>0.3910218821302678</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9518815807886867</v>
+        <v>0.8822428700477403</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4840906795066786</v>
+        <v>0.4179550421221165</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4433080463794425</v>
+        <v>0.4196153914878096</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2070357195497863</v>
+        <v>-0.2284785648863163</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.05843380036927925</v>
+        <v>-0.0820121462445158</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1648705023466093</v>
+        <v>-0.1845577616306713</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1966074804946487</v>
+        <v>-0.2142901839948053</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1441459066997055</v>
+        <v>0.1500377280593383</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2305668500358706</v>
+        <v>-0.219189069587344</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1507177033492937</v>
+        <v>-0.1359203168764012</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.263090284136851</v>
+        <v>-0.269302423202511</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.000717</t>
+          <t>X &gt; 0.0007157</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5666740703505795</v>
+        <v>-0.6526054635638232</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2490623299258203</v>
+        <v>0.1560749576416356</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2908474931797471</v>
+        <v>0.1694616512607823</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7047013284866779</v>
+        <v>0.6046892039258438</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.0411234632136086</v>
+        <v>-0.08812227799300132</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.008372652204421627</v>
+        <v>-0.06978968538271602</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4068006171792931</v>
+        <v>-0.4866798713002964</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1288510879996778</v>
+        <v>-0.2121116221636754</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.03614471993230239</v>
+        <v>-0.1192380857545103</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.0872971394755524</v>
+        <v>0.002406233457136864</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.497350079576016</v>
+        <v>0.4387366185331345</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>-0.0354416575790637</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.009118362224477039</v>
+        <v>-0.04465194321821997</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.0299359796641312</v>
+        <v>-0.02213548967458223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001613</t>
+          <t>X &gt; 0.001611</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8319172083906565</v>
+        <v>-0.92374284721366</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7104906872444872</v>
+        <v>0.6658180229771347</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4659566803260233</v>
+        <v>0.3308344412429278</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9235876234357292</v>
+        <v>0.8132449219405657</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1227716453035583</v>
+        <v>-0.02853065849431147</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3935760999611873</v>
+        <v>0.3030092669051143</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.07234516947745107</v>
+        <v>-0.1689276683838017</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.2616565173555685</v>
+        <v>0.1878012633597663</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.03587206140257138</v>
+        <v>-0.1106129115664274</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2969412534443947</v>
+        <v>0.2155740693988619</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5653329396549225</v>
+        <v>0.5153632690600816</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.06748164198068451</v>
+        <v>0.01798253895467639</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.0569861835385197</v>
+        <v>-0.1083923276398124</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.2452067722238738</v>
+        <v>-0.2977946143108099</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002508</t>
+          <t>X &gt; 0.002507</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7592013432539559</v>
+        <v>-0.8633003322450747</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.25248296782236</v>
+        <v>1.127453907055973</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.459643029296316</v>
+        <v>1.294332597087454</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.347576987347821</v>
+        <v>1.213985383922306</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.355238262548184</v>
+        <v>0.1641195646242082</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.973663192169461</v>
+        <v>0.8573675922027704</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.01073916111810291</v>
+        <v>-0.1142905993352343</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.4297531539193642</v>
+        <v>0.330878742593967</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1569065906169271</v>
+        <v>0.08367487907735693</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2250668903322719</v>
+        <v>0.1400852483444908</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5147160145579548</v>
+        <v>0.4665419809958991</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1959868222805028</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1535425621063453</v>
+        <v>-0.2124989918328737</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.06904984973292017</v>
+        <v>-0.0645163455954787</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.003404</t>
+          <t>X &gt; 0.003402</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.561195262646045</v>
+        <v>-0.5970683466261164</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9297319375371842</v>
+        <v>0.8632328290876004</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.719420197940487</v>
+        <v>1.512973101642466</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.111418126923681</v>
+        <v>1.034161490683225</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.09630551471388316</v>
+        <v>-0.06378330244260866</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.9677297138779508</v>
+        <v>0.7307413468111008</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.05456785777153073</v>
+        <v>-0.1994799598056574</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4646921964409216</v>
+        <v>0.29120901894143</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3857636442923749</v>
+        <v>-0.5283722858475386</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1830508616748716</v>
+        <v>-0.3087226057929584</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5771602607666892</v>
+        <v>0.4929264801026747</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2656545693341243</v>
+        <v>-0.3577413091470092</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5980861244019238</v>
+        <v>-0.7914788966350983</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8109469654034598</v>
+        <v>-0.8428611295072201</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0043</t>
+          <t>X &gt; 0.004298</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.659448341596779</v>
+        <v>-1.636749379472136</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.03508457973853041</v>
+        <v>-0.1631579056760231</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8369464696928901</v>
+        <v>0.6439774684546862</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6982966901802001</v>
+        <v>0.555520898315649</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.319580382106977</v>
+        <v>-1.571282827789105</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3024097032034447</v>
+        <v>-0.5343051692321907</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.7682720424199658</v>
+        <v>-1.140812786841927</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4184630624151211</v>
+        <v>0.1400793436044268</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8553085097636668</v>
+        <v>-1.097766627977791</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9334522234033287</v>
+        <v>-1.157403069054773</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.07463603399247631</v>
+        <v>-0.09946319588072328</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3320001466180145</v>
+        <v>-0.5270015200360731</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5316438334485127</v>
+        <v>-0.7517543330084777</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1956545999805215</v>
+        <v>-0.3319306619771396</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.005196</t>
+          <t>X &gt; 0.005193</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.3844134823596335</v>
+        <v>0.2716285460117263</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.148930874967093</v>
+        <v>1.969478564992833</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.840712698543335</v>
+        <v>2.431660690800804</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.758459548904199</v>
+        <v>1.420317913185244</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7162635662755434</v>
+        <v>-1.208731513073381</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5250912344296523</v>
+        <v>0.0626274722220046</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4915228024049298</v>
+        <v>-0.9966020834799139</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6310039295308698</v>
+        <v>0.3920587367358905</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1525215795930634</v>
+        <v>-0.3581806341698126</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7134230348824531</v>
+        <v>-0.8967025102772368</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.09343650049897434</v>
+        <v>-0.02217982351538694</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5947286997468595</v>
+        <v>-0.7420633620548429</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.4302071521420459</v>
+        <v>0.2314961997293992</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.3669254613281154</v>
+        <v>0.2749937509202383</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.006091</t>
+          <t>X &gt; 0.006089</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.953866578161303</v>
+        <v>2.824427053955695</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.258170108706722</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.14949012801042</v>
+        <v>2.836662070901049</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.656102090608549</v>
+        <v>2.243218806509937</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.579514636883971</v>
+        <v>0.1264832279450019</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.258011980147479</v>
+        <v>1.665091531574056</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.09428252906514</v>
+        <v>1.423603615947158</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.909265167329693</v>
+        <v>2.404425466775386</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.566231728755625</v>
+        <v>1.101630072828456</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1668623829752178</v>
+        <v>-0.2646939871908671</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.244212506766303</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.3628397433707136</v>
+        <v>0.05255006084744451</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.0415899889584</v>
+        <v>0.6667558734666486</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.9010252728845671</v>
+        <v>0.6561076155348147</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.006987</t>
+          <t>X &gt; 0.006984</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.494987583923482</v>
+        <v>1.206914554009899</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.120458262875253</v>
+        <v>3.700476077966748</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.898114385109245</v>
+        <v>2.347505475743176</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.575555025065647</v>
+        <v>1.038540596094549</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2832874324236627</v>
+        <v>-0.8895574657206851</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.093433678684505</v>
+        <v>1.301693280915991</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.146994045191285</v>
+        <v>1.241037191690531</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.387242474575281</v>
+        <v>2.693669659124929</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.375040805857381</v>
+        <v>0.7382318221703912</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2812195705031328</v>
+        <v>-0.3254049121218117</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.53993304638928</v>
+        <v>1.149111714682633</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1108965645982636</v>
+        <v>-0.3376394597768595</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.641965223479978</v>
+        <v>1.088333290211672</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4042862395601645</v>
+        <v>0.02720994315887992</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.007883</t>
+          <t>X &gt; 0.00788</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.240766817362079</v>
+        <v>1.038275271887215</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.700105668609616</v>
+        <v>3.326065928666843</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.681957660477948</v>
+        <v>1.31942471454569</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.487507479390985</v>
+        <v>1.126728110599075</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3494833724060129</v>
+        <v>-0.6528436109979978</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1255631476051562</v>
+        <v>-0.3800580921790697</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.853673464926665</v>
+        <v>1.172189044401918</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.366996978002668</v>
+        <v>1.996678864663728</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.998825278996236</v>
+        <v>0.6693836748817787</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.8025012539082041</v>
+        <v>0.4907163843893798</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.558584409373509</v>
+        <v>2.544640452982307</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.612570404866091</v>
+        <v>1.498307764519879</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.480001250899079</v>
+        <v>3.238231584688279</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.744952587400128</v>
+        <v>1.539224498651706</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.008779</t>
+          <t>X &gt; 0.008775</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.56110077618834</v>
+        <v>2.30160365628457</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.401568762477766</v>
+        <v>4.902526989538757</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.319033664642568</v>
+        <v>2.835148833860032</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.183436023420796</v>
+        <v>1.709802749551699</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3793236855149758</v>
+        <v>-0.03467651692322704</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2547567868800158</v>
+        <v>-0.1803010399453129</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.6736579558982</v>
+        <v>1.01427299635224</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.32523337990807</v>
+        <v>3.058900487014931</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.993064782707329</v>
+        <v>1.766697752355121</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.143145986377469</v>
+        <v>0.9428691715401385</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.752004150151173</v>
+        <v>4.922829142414088</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.244009421150565</v>
+        <v>2.296491115530188</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.518773822074436</v>
+        <v>3.413583658774535</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.625865404504367</v>
+        <v>1.552923879439696</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.009674</t>
+          <t>X &gt; 0.009671</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>184</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.866910056422164</v>
+        <v>1.837714262069532</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.603550050314865</v>
+        <v>4.60236326387021</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.491387361211999</v>
+        <v>1.491233971207677</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.1827353212866</v>
+        <v>-2.183229813664603</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.634068352643155</v>
+        <v>-1.585522432877383</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.423650844747208</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3344481605351177</v>
+        <v>-0.2864364815447971</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8289179782868459</v>
+        <v>0.8781655406805626</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.405977221714195</v>
+        <v>-1.332720111934499</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.6254612354353526</v>
+        <v>-0.5261139101407792</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.430707171521846</v>
+        <v>2.530615207540521</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.339262502209792</v>
+        <v>-1.215565881181547</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1289785729145052</v>
+        <v>0.01971097486332241</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.9901994444270983</v>
+        <v>-0.818200684860436</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.76046327981048</v>
+        <v>4.731267485457849</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.528587531574225</v>
+        <v>4.527400745129569</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.762735577318736</v>
+        <v>-2.762888967323057</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.322165606144168</v>
+        <v>-3.322660098522171</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.550110331653656</v>
+        <v>-4.501564411887884</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.942391474432362</v>
+        <v>-4.918434065482749</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.57882597162957</v>
+        <v>-1.530814292639249</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6665842705887215</v>
+        <v>-0.6173367081950047</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.175842289180459</v>
+        <v>-4.102585179400762</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.267140395855151</v>
+        <v>-2.167793070560577</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.666089480367425</v>
+        <v>1.765997516386101</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.43746340176002</v>
+        <v>-2.313766780731775</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7886487378320481</v>
+        <v>-0.6399591900542205</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.011188949674477</v>
+        <v>-3.839190190107814</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.01147</t>
+          <t>X &gt; 0.01146</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>115</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.649518752074343</v>
+        <v>6.620322957721712</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.4296370068366</v>
+        <v>2.428450220391944</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.312960464874962</v>
+        <v>-2.313113854879283</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.530561408243116</v>
+        <v>-6.531055900621119</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-7.938416178730115</v>
+        <v>-7.889870258964343</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.901911714312419</v>
+        <v>-5.877954305362806</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.377926421404673</v>
+        <v>-3.329914742414353</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.975429847800115</v>
+        <v>-2.926182285406398</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-8.253803308670712</v>
+        <v>-8.180546198891015</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.495026452826657</v>
+        <v>-6.395679127532084</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.482336306739029</v>
+        <v>-1.382428270720354</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.665349458731527</v>
+        <v>-6.541652837703282</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.607239442479717</v>
+        <v>-3.458549894701889</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.859764661818403</v>
+        <v>-6.687765902251741</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.214736143378694</v>
+        <v>6.185540349026063</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.4296370068366</v>
+        <v>2.428450220391944</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.312960464874962</v>
+        <v>-2.313113854879283</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-5.443604886503991</v>
+        <v>-5.444099378881994</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-8.155807483077943</v>
+        <v>-8.107261563312171</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.945389975181989</v>
+        <v>-8.921432566232376</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.856187290969892</v>
+        <v>-6.808175611979571</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-8.410212456495763</v>
+        <v>-8.360964894102047</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.73206417823593</v>
+        <v>-11.65880706845623</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-9.321113409348399</v>
+        <v>-9.221766084053826</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.091031958912943</v>
+        <v>-3.991123922894268</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.404479893514136</v>
+        <v>-8.280783272485891</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.511938574861887</v>
+        <v>-7.339939815295224</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01326</t>
+          <t>X &gt; 0.01325</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>8.233369683751356</v>
+        <v>8.204173889398724</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.431707400211344</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.166172174288668</v>
+        <v>-3.166666666666671</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.085414108336742</v>
+        <v>-6.036868188570971</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-8.168992459654035</v>
+        <v>-8.145035050704422</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-5.872750437967824</v>
+        <v>-5.824738758977503</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-7.530295272230759</v>
+        <v>-7.481047709837043</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-11.16270600018211</v>
+        <v>-11.08944889040241</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-9.631672415559578</v>
+        <v>-9.532325090265005</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-3.883992621438814</v>
+        <v>-3.784084585420139</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-9.801995421464447</v>
+        <v>-9.678298800436202</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-8.805934434075141</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.23495926645533</v>
+        <v>-11.23614605289998</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-11.499505507622</v>
+        <v>-11.50000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.656842679765312</v>
+        <v>-9.60829675999954</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.407087697749276</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4484202858963826</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.298339082226242</v>
+        <v>-1.198991756931669</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2781858976549216</v>
+        <v>-0.154489276626677</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="7">
@@ -3960,49 +3960,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.326444485818904</v>
+        <v>-4.929466663596656</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.311614318720132</v>
+        <v>-5.706192135849285</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.8283369229873614</v>
+        <v>-1.261220446744645</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.763152429805508</v>
+        <v>-5.163594470046085</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.488433852819902</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.939027302859607</v>
+        <v>-1.347800027662956</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.210729532044482</v>
+        <v>-0.6020045039851851</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.574234344493988</v>
+        <v>2.964420800147607</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07422779772731047</v>
+        <v>0.508093352301124</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.03731713147875126</v>
+        <v>0.4907163843893798</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.271640363462453</v>
+        <v>2.705930775562962</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.306018515817776</v>
+        <v>2.764097512927854</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2598514023417664</v>
+        <v>0.7560363605575802</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4855870525682988</v>
+        <v>1.005081222572947</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>151</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.487538547090637</v>
+        <v>-1.516734341443268</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.760976295783607</v>
+        <v>-3.762163082228263</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1822377467638177</v>
+        <v>-0.182391136768139</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.025522536950284</v>
+        <v>-4.026017029328287</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.901560434416837</v>
+        <v>-3.853014514651065</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.693826840251354</v>
+        <v>1.717784249200967</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.609116480985186</v>
+        <v>1.657128159975507</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.128802804085865</v>
+        <v>3.178050366479582</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.743317336304813</v>
+        <v>1.816574446084509</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.555650195604088</v>
+        <v>1.654997520898661</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.33770400423132</v>
+        <v>3.437612040249995</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.034333812215777</v>
+        <v>4.158030433244022</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.627427992014951</v>
+        <v>1.776117539792779</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.5286603309832074</v>
+        <v>0.7006590905498697</v>
       </c>
     </row>
     <row r="9">
@@ -4067,254 +4067,254 @@
         <v>192</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.522582697201024</v>
+        <v>-3.551778491553655</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.529602123598181</v>
+        <v>-2.530788910042837</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2006264916467799</v>
+        <v>0.2004731016424586</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.752481698098194</v>
+        <v>-1.752976190476197</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.769937917860553</v>
+        <v>-1.721391998094781</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.17326944510787</v>
+        <v>2.197226854057483</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.088559085841702</v>
+        <v>2.136570764832022</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.704823775388292</v>
+        <v>3.754071337782008</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.123008285532187</v>
+        <v>3.196265395311883</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.314756155868992</v>
+        <v>3.414103481163565</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.589221664275463</v>
+        <v>2.689129700294139</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.144433149964122</v>
+        <v>3.268129770992367</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.161782296650713</v>
+        <v>1.310471844428541</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3458512802105815</v>
+        <v>0.5178500397772439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.009136</t>
+          <t>X &lt; -0.009135</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>261</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7567780994998685</v>
+        <v>-0.7859738938524998</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.367964192563697</v>
+        <v>-2.369150979008353</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6855402847502248</v>
+        <v>0.6853868947459034</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.8157654283385867</v>
+        <v>0.8152709359605836</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8719494121134233</v>
+        <v>-0.8234034923476514</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.256423070516021</v>
+        <v>1.304434749506342</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.854488526346145</v>
+        <v>3.903736088739862</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.494655795110731</v>
+        <v>1.567912904890427</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.411020523685082</v>
+        <v>1.510367848979655</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.589461127877001</v>
+        <v>1.689369163895677</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.00698104268443</v>
+        <v>2.130677663712675</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-0.9464726000159018</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1031429726629867</v>
+        <v>0.06885578690367566</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.00824</t>
+          <t>X &lt; -0.008239</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>329</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2012807721756928</v>
+        <v>-0.2304765665283242</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.812466865239521</v>
+        <v>-1.813653651684177</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.440178163379301</v>
+        <v>1.440024773374979</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5572562675004136</v>
+        <v>-0.5577507598784166</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.7915944528149552</v>
+        <v>-0.7430485330491834</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1902690553987156</v>
+        <v>-0.1663116464491026</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.244777424240887</v>
+        <v>1.292789103231208</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.905368354922238</v>
+        <v>2.954615917315955</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.994467402069603</v>
+        <v>2.093814727364176</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.78976624380941</v>
+        <v>1.889674279828085</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.520193028383581</v>
+        <v>1.643889649411825</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.419714663835606</v>
+        <v>-0.2710251160577783</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4139237219532319</v>
+        <v>0.5859224815198942</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.007345</t>
+          <t>X &lt; -0.007344</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>402</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4908662792905716</v>
+        <v>-0.5200620736432029</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8582712778270363</v>
+        <v>-0.859458064271692</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.9857633075671757</v>
+        <v>0.9856099175628543</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3765488622772892</v>
+        <v>-0.3770433546552923</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6660821964675208</v>
+        <v>-0.6175362767017489</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.128804270978506</v>
+        <v>0.1527616799281191</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.039118787334239</v>
+        <v>1.08713046632456</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.562099894791281</v>
+        <v>2.611347457184998</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.003605300457551</v>
+        <v>2.076862410237247</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.397467598655055</v>
+        <v>2.496814923949628</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7002291269620358</v>
+        <v>0.800137162980711</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.9833634982228219</v>
+        <v>1.107060119251067</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.178080887428891</v>
+        <v>-1.029391339651063</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4548327993914185</v>
+        <v>-0.2828340398247562</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.006449</t>
+          <t>X &lt; -0.006448</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>489</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8933170983000096</v>
+        <v>0.8641213039473783</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5091248702668452</v>
+        <v>0.5079380838221894</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.363842238068045</v>
+        <v>2.363688848063724</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6535765841103967</v>
+        <v>0.6530820917323936</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3197860085198201</v>
+        <v>0.3683319282855919</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.43515594817535</v>
+        <v>1.459113357124963</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.168441498929631</v>
+        <v>2.216453177919952</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.35985956270936</v>
+        <v>4.409107125103077</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.094378428681473</v>
+        <v>4.16763553846117</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.653457587361828</v>
+        <v>3.752804912656401</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.630760519081193</v>
+        <v>2.730668555099868</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.074136626446744</v>
+        <v>3.197833247474989</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.835989863112886</v>
+        <v>1.984679410890713</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.67522244585475</v>
+        <v>2.847221205421413</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>607</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4216079580467138</v>
+        <v>-0.4508037523993451</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6031202816736467</v>
+        <v>0.601933495228991</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.514773938104774</v>
+        <v>2.514620548100453</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3385740405069697</v>
+        <v>0.3380795481289667</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2945184248083095</v>
+        <v>0.3430643445740813</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.745104975036483</v>
+        <v>1.769062383986096</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.648862490564376</v>
+        <v>2.696874169554697</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.488218887963804</v>
+        <v>4.53746645035752</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.086215314637073</v>
+        <v>5.159472424416769</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.06001974730227</v>
+        <v>5.159367072596844</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.525829297444062</v>
+        <v>4.625737333462737</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.39546280400036</v>
+        <v>4.519159425028604</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.645822659088935</v>
+        <v>3.794512206866763</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.189515475707559</v>
+        <v>5.361514235274221</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>754</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.099985826229577</v>
+        <v>1.070790031876946</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.212937664200226</v>
+        <v>1.21175087775557</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.409678215784716</v>
+        <v>2.409524825780395</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.346269407118427</v>
+        <v>1.345774914740424</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4101018699378542</v>
+        <v>0.4586477897036261</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.431613830607425</v>
+        <v>2.455571239557038</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.877407450121098</v>
+        <v>2.925419129111418</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.399728726758759</v>
+        <v>4.448976289152476</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.134502538405748</v>
+        <v>5.207759648185444</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.080339710245653</v>
+        <v>5.179687035540226</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.610386562595536</v>
+        <v>4.710294598614212</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.379512725560943</v>
+        <v>4.503209346589188</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.561483888162648</v>
+        <v>3.710173435940476</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.980853490643817</v>
+        <v>5.152852250210479</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>946</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.218872552975157</v>
+        <v>1.287356529543395</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5590606670994873</v>
+        <v>0.6535465329951435</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.432788225262001</v>
+        <v>1.479182182951853</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.668721614093492</v>
+        <v>1.668227121715489</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.341848551484063</v>
+        <v>1.390394471249834</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.802013278793559</v>
+        <v>2.825970687743173</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.351552390986171</v>
+        <v>3.399564069976492</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.04727444487385</v>
+        <v>4.096522007267566</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.254791231268612</v>
+        <v>5.328048341048309</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.03912190639754</v>
+        <v>5.138469231692113</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.411587767164825</v>
+        <v>4.5114958031835</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.974507145735799</v>
+        <v>5.098203766764044</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.448648047179262</v>
+        <v>4.597337594957089</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.837174395080197</v>
+        <v>6.009173154646859</v>
       </c>
     </row>
     <row r="17">
@@ -4483,774 +4483,774 @@
         <v>1194</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.282903064943028</v>
+        <v>0.3720936888974791</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5142630355307958</v>
+        <v>0.588985337448797</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9570125887992091</v>
+        <v>0.9941446497596189</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.003485638585225</v>
+        <v>1.002991146207222</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.135212835908298</v>
+        <v>1.18375875567407</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.767595240752762</v>
+        <v>1.791552649702375</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.352901631905347</v>
+        <v>2.400913310895668</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.058362301351437</v>
+        <v>3.107609863745154</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.918653176654459</v>
+        <v>3.991910286434155</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.073759505952744</v>
+        <v>4.173106831247317</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.366545784878483</v>
+        <v>3.466453820897158</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.652180218640837</v>
+        <v>3.775876839669081</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.980773083920397</v>
+        <v>3.129462631698225</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.044029672170375</v>
+        <v>4.216028431737037</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.00197</t>
+          <t>X &lt; -0.001971</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9250785198743685</v>
+        <v>0.9909078895929611</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2092683361322401</v>
+        <v>-0.1477106787503217</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2133989712108075</v>
+        <v>0.2440827000086898</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.003024659758303017</v>
+        <v>0.002530167380299986</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3502936897688755</v>
+        <v>0.3988396095346474</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4433080463794425</v>
+        <v>0.4672654553290556</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.107916488203188</v>
+        <v>1.155928167193508</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.117687081473676</v>
+        <v>1.166934643867393</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.185721305300419</v>
+        <v>2.219880290861376</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.534571981244163</v>
+        <v>2.55408985718536</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.579529758863913</v>
+        <v>1.600630608559349</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.954972031273805</v>
+        <v>1.999396800965116</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.261969881916748</v>
+        <v>1.331759310368597</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.169833772252417</v>
+        <v>2.262003082465704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001074</t>
+          <t>X &lt; -0.001075</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1727</v>
+        <v>1732</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5791301588420907</v>
+        <v>0.6004872534540269</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.281478567016201</v>
+        <v>-0.2604358841062364</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2720929078913201</v>
+        <v>-0.2194375096608852</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.181128734279866</v>
+        <v>-1.154603907344821</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.737894037952934</v>
+        <v>-0.6628951717820328</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9024137727520198</v>
+        <v>-0.8517368889700236</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2365467648126511</v>
+        <v>-0.1885350858223305</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2417216441652172</v>
+        <v>-0.1924740817715005</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4800273496569716</v>
+        <v>0.5211306762972541</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5871549997996297</v>
+        <v>0.6210896243506312</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.04747825860867039</v>
+        <v>-0.04494458761963926</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6560072240381913</v>
+        <v>0.648326075842256</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.268795904062415</v>
+        <v>0.2531681492784301</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9577625907683824</v>
+        <v>0.96410677572797</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0001787</t>
+          <t>X &lt; -0.0001798</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5317421973137471</v>
+        <v>0.5975182913333299</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1680514906867927</v>
+        <v>-0.09935564411765796</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4109241412646156</v>
+        <v>-0.3646192099407486</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9389268457775231</v>
+        <v>-0.8652400231347599</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4139252596327054</v>
+        <v>-0.3423434150988243</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3190828755672328</v>
+        <v>-0.2951254666176197</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4569662588374754</v>
+        <v>0.4822521224814622</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2936950834051686</v>
+        <v>0.3203707298792722</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.4634338174470756</v>
+        <v>0.4860323659299155</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5033648735577856</v>
+        <v>0.5233993271615418</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1245073302659989</v>
+        <v>0.1166246344380113</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5426447176962412</v>
+        <v>0.5294013008809131</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4558812814222861</v>
+        <v>0.4381947420982399</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.5800940890092292</v>
+        <v>0.5859224815198942</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.000717</t>
+          <t>X &lt; 0.0007157</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2217</v>
+        <v>2222</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5105369609186425</v>
+        <v>0.5868361104810589</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.06601125540205288</v>
+        <v>0.01537745726744788</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1908771070936623</v>
+        <v>-0.08451117508710126</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.4245585874799431</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.07582231605757528</v>
+        <v>0.1895792249268027</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1482750681398031</v>
+        <v>0.2172167325999865</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5583915194899234</v>
+        <v>0.6312639841539536</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3162441532560436</v>
+        <v>0.3904537260208372</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2802240071043443</v>
+        <v>0.3534811168840406</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.1756859172377432</v>
+        <v>0.2497245432697781</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.1838639213101132</v>
+        <v>-0.1344339060664979</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2363101215729628</v>
+        <v>0.2837688348987584</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2473886988148308</v>
+        <v>0.29365141238533</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2281528138145532</v>
+        <v>0.2726692717004298</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001613</t>
+          <t>X &lt; 0.001611</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2478</v>
+        <v>2484</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5786652899165361</v>
+        <v>0.6412330165421665</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3481407709411712</v>
+        <v>-0.318188508436414</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2598203682566051</v>
+        <v>-0.1680232824475425</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5321717142012545</v>
+        <v>-0.4584290307763013</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.01649525444218369</v>
+        <v>0.1194302777395606</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1289648544090412</v>
+        <v>-0.06837719528551389</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.2291589248111023</v>
+        <v>0.2953148962874224</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.003636174744173104</v>
+        <v>0.05288373713788985</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2467832888883379</v>
+        <v>0.2977146706742033</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.02355954023644102</v>
+        <v>0.07775082415874124</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1585362962243337</v>
+        <v>-0.1263896233773494</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1807234725447628</v>
+        <v>0.2135806566606391</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2673944386434499</v>
+        <v>0.3015145175364253</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.3950340889272894</v>
+        <v>0.4297864326918912</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002508</t>
+          <t>X &lt; 0.002507</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2753</v>
+        <v>2758</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.4005627661311095</v>
+        <v>0.4544579509626203</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5219680170378282</v>
+        <v>-0.4585691993737626</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6992693039313309</v>
+        <v>-0.6158257406151435</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6052891766532227</v>
+        <v>-0.5388294297089118</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.0924732567514539</v>
+        <v>0.005164844772707511</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3750194880804898</v>
+        <v>-0.317902024368216</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1564354299277184</v>
+        <v>0.2208098952668038</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.05691809968721628</v>
+        <v>-0.007670537293499535</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1196241907775288</v>
+        <v>0.1566231424716591</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.08774309819761328</v>
+        <v>0.1304740395391946</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.06030059019961698</v>
+        <v>-0.03740824991131575</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1033714439750071</v>
+        <v>0.1295329617102752</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2846490359390188</v>
+        <v>0.3145055645155566</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2404738132048863</v>
+        <v>0.2372270037608075</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.003404</t>
+          <t>X &lt; 0.003402</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3029</v>
+        <v>3034</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.220006235605311</v>
+        <v>0.2338908040975696</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2383471828867201</v>
+        <v>-0.2142619540927981</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.6001804912254229</v>
+        <v>-0.5245145668876248</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3382030419717097</v>
+        <v>-0.3110902255639161</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.04577354459004823</v>
+        <v>0.1058949383974834</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2497378012689495</v>
+        <v>-0.1628099025806549</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1266849092936084</v>
+        <v>0.2225039774321758</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.02578440692911954</v>
+        <v>0.03824459206396114</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3269195138336514</v>
+        <v>0.3818776962454251</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2536368020938511</v>
+        <v>0.3014634020600724</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.03143576756270505</v>
+        <v>-0.001556412648071159</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.2854344696605935</v>
+        <v>0.3202886371756222</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4119885672777741</v>
+        <v>0.4854471245867487</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4914920307333048</v>
+        <v>0.5037734632006661</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0043</t>
+          <t>X &lt; 0.004298</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3262</v>
+        <v>3268</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4710570499183859</v>
+        <v>0.4651704454822578</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1140771361142683</v>
+        <v>0.1496903329364017</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.1889230647924904</v>
+        <v>-0.1358818601896061</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1198787104363177</v>
+        <v>-0.0810280129156169</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4430859426472509</v>
+        <v>0.5156611641416973</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1898328691927063</v>
+        <v>0.2552443764698751</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.3498456668552663</v>
+        <v>0.4559239188114432</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.02201573785259114</v>
+        <v>0.09868142952512926</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4064487507908296</v>
+        <v>0.4762694740311559</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4308767927336561</v>
+        <v>0.4956518287767864</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1515940481447871</v>
+        <v>0.1997121156348243</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2645311891798059</v>
+        <v>0.3190783634036265</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3213938504355767</v>
+        <v>0.3829167648691794</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2273784618987094</v>
+        <v>0.2647645644610392</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.005196</t>
+          <t>X &lt; 0.005193</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3477</v>
+        <v>3483</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.06989421652746586</v>
+        <v>-0.04733977448606197</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3320561993731488</v>
+        <v>-0.2978148338468998</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5259090996276186</v>
+        <v>-0.446912285177028</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2808733934674947</v>
+        <v>-0.2155550096220864</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2141321165826113</v>
+        <v>0.314158460620817</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.005141385355202033</v>
+        <v>0.08655985281476575</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2258773024509608</v>
+        <v>0.3284454062548505</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.004260324340343402</v>
+        <v>0.05055029521864185</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.1888708166445667</v>
+        <v>0.2303258622081756</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3028702035564379</v>
+        <v>0.3411419537446676</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1431009746202889</v>
+        <v>0.1657123876326452</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2799246705160101</v>
+        <v>0.310011769269714</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.07728689699574431</v>
+        <v>0.1158300126743015</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.08925435757613087</v>
+        <v>0.1064769418731331</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.006091</t>
+          <t>X &lt; 0.006089</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3623</v>
+        <v>3630</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4423485374214025</v>
+        <v>-0.4221997369748891</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4006420685017602</v>
+        <v>-0.3697384841016458</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4372867314937139</v>
+        <v>-0.3913699439870086</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3346097972717459</v>
+        <v>-0.274107388349897</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.01890486000931446</v>
+        <v>0.04909755086011103</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.244946808335655</v>
+        <v>-0.1582007021094185</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.191916120769875</v>
+        <v>-0.0938112751606397</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3132999042296021</v>
+        <v>-0.2418514532997449</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.08353342707346911</v>
+        <v>-0.01592256357211141</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1294446036219554</v>
+        <v>0.1944325916014549</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.03218162677067937</v>
+        <v>0.005761931699105105</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1004676327227472</v>
+        <v>0.1465732971631653</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.000607328073343183</v>
+        <v>0.05444567362964392</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.01995308350435465</v>
+        <v>0.05555665134748722</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.006987</t>
+          <t>X &lt; 0.006984</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3759</v>
+        <v>3766</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1581127387902583</v>
+        <v>-0.1266372486158005</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3623436951405168</v>
+        <v>-0.3184544729567449</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2792812598796317</v>
+        <v>-0.2209961617385687</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1081088002401671</v>
+        <v>-0.050225284919172</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.09709607045596158</v>
+        <v>0.1642124557758464</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1365973454745344</v>
+        <v>-0.05225935649674796</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.115094215627586</v>
+        <v>-0.01887795311670004</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2489444849038662</v>
+        <v>-0.1783654270539259</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.003098692859595076</v>
+        <v>0.06463057577897047</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1183370753481299</v>
+        <v>0.1845773330350866</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.01826770308232284</v>
+        <v>0.02189877446655686</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.1374203874009794</v>
+        <v>0.1862790009445661</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.02837727781736987</v>
+        <v>0.03010142488525247</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.106010232059468</v>
+        <v>0.1463794255092381</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.007883</t>
+          <t>X &lt; 0.00788</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3863</v>
+        <v>3872</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.092586570167704</v>
+        <v>-0.07642653001188648</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.206225542136778</v>
+        <v>-0.1777814396667452</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.0963776405846275</v>
+        <v>-0.0680627138690042</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.05543420821616252</v>
+        <v>-0.02724594992636753</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.09214218549862352</v>
+        <v>0.1162272336659882</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.07943869575386486</v>
+        <v>0.1195343149479768</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.03111145679396543</v>
+        <v>0.02139902551467543</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.07051115181081258</v>
+        <v>-0.04333578296103013</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.06371838549770814</v>
+        <v>0.08873851359145135</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08146807725507443</v>
+        <v>0.1051850506008378</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.05697811154794863</v>
+        <v>-0.05865948121890341</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.01781607363812299</v>
+        <v>0.02532703409590198</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1289785729145052</v>
+        <v>-0.1116331129688248</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.007842176750401109</v>
+        <v>0.02284315272490289</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.008779</t>
+          <t>X &lt; 0.008775</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3933</v>
+        <v>3943</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.148258829722991</v>
+        <v>-0.1327724217509143</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2381467483446329</v>
+        <v>-0.2101621708574086</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1627548170014563</v>
+        <v>-0.1348001777097636</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.06948448855988687</v>
+        <v>-0.04177965795278027</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.0403576923906499</v>
+        <v>0.06500040696850817</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.07248687319584945</v>
+        <v>0.09846239892115705</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.0131572245895768</v>
+        <v>0.05165435145816133</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.0846056483233113</v>
+        <v>-0.07095927618640729</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.02075671959347147</v>
+        <v>0.03272425660602352</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.07386842409352568</v>
+        <v>0.08473085758942034</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1419775227164024</v>
+        <v>-0.1559091773258743</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.008314979697289004</v>
+        <v>0.003677438335166983</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.06708781011085563</v>
+        <v>-0.06186588376618829</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.04590531021312216</v>
+        <v>0.04932459383929455</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.009674</t>
+          <t>X &lt; 0.009671</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3985</v>
+        <v>3996</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.07971543023420935</v>
+        <v>-0.07808388774554942</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.126628018018998</v>
+        <v>-0.1262230417793617</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.03241905389876365</v>
+        <v>-0.03232263082572473</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1614993198408996</v>
+        <v>0.1610798088581404</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1376109053742951</v>
+        <v>0.1348814101449278</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1983289241962751</v>
+        <v>0.1966232909539229</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1273449909853213</v>
+        <v>0.1246682333972586</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.07491168151040739</v>
+        <v>0.07231846421878885</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2032087867853249</v>
+        <v>0.1990980204889254</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1693876424571101</v>
+        <v>0.1641034811635649</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.02893664254360573</v>
+        <v>0.02401029544292754</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2028417278422339</v>
+        <v>0.1962813467802604</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1480780818990795</v>
+        <v>0.1404537058245836</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1873140572912959</v>
+        <v>0.1784481378753426</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4024</v>
+        <v>4035</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1648397362564253</v>
+        <v>-0.1632738802229596</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07822699971314506</v>
+        <v>-0.07796891992669686</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1351834928859361</v>
+        <v>0.1348218411382547</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1797918930437703</v>
+        <v>0.1793219141797593</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2253199546908959</v>
+        <v>0.2228463797489368</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2635472228856486</v>
+        <v>0.2619117002937799</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1676389254183164</v>
+        <v>0.1653415878569291</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1360169102104578</v>
+        <v>0.1337576777968579</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2873170470114559</v>
+        <v>0.2837241411864753</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2207889264747465</v>
+        <v>0.2163750830452145</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.07972845179305921</v>
+        <v>0.07567625799597266</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2274560014295943</v>
+        <v>0.2220869173882107</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1691580730482229</v>
+        <v>0.1629867106327083</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2847594975730701</v>
+        <v>0.2773760620820767</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.01147</t>
+          <t>X &lt; 0.01146</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4054</v>
+        <v>4065</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.181924144623359</v>
+        <v>-0.1805385046319543</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.0151285699581365</v>
+        <v>0.01512413876756113</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1010723711055803</v>
+        <v>0.1008043087082129</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2447295879910456</v>
+        <v>0.2440841367221651</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.285962894347179</v>
+        <v>0.2837012763283937</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.252263782872518</v>
+        <v>0.2508472403411446</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2056843833874638</v>
+        <v>0.2036549167639166</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1954846949285312</v>
+        <v>0.1934443419578855</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3698671177568684</v>
+        <v>0.3666175656640576</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3222105669089075</v>
+        <v>0.3182875558747966</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1807044923093244</v>
+        <v>0.1771459244829288</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.3276185543033705</v>
+        <v>0.3229306069894093</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2420073274768555</v>
+        <v>0.2367814853532764</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.3337747303010232</v>
+        <v>0.3275825121019622</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4077</v>
+        <v>4088</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1337277664756797</v>
+        <v>-0.1326429148650448</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.02870981086012137</v>
+        <v>0.02866230946936099</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.08749048381899627</v>
+        <v>0.08725951296229795</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1821331375595818</v>
+        <v>0.1816565572055993</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2445628163538345</v>
+        <v>0.2426975796450321</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2861570420070976</v>
+        <v>0.2847919582241474</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2638569963869131</v>
+        <v>0.2619523277135869</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3000815515332818</v>
+        <v>0.2980482959321549</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3996700526398058</v>
+        <v>0.3967703224232011</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3474993560650148</v>
+        <v>0.3440888184069735</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2301530368244826</v>
+        <v>0.2270432096235595</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3274130469977052</v>
+        <v>0.3234476194031259</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.288958608568322</v>
+        <v>0.2844722112663973</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3079097791068293</v>
+        <v>0.3027897005730722</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01326</t>
+          <t>X &lt; 0.01325</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4085</v>
+        <v>4096</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1627120285821775</v>
+        <v>-0.161608539416072</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.02815289245344132</v>
+        <v>-0.02805035113339471</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.02972805414677993</v>
+        <v>0.02965194264562143</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1244261163096212</v>
+        <v>0.1241040985317596</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1856678466729136</v>
+        <v>0.1840586718199617</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.252179576226041</v>
+        <v>0.2509549242329214</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.229749212918918</v>
+        <v>0.2280333125613225</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2649812348521579</v>
+        <v>0.2631421162640493</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.3642470793382131</v>
+        <v>0.3615909256703347</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.3349628078621478</v>
+        <v>0.3317864079928299</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2174424731469671</v>
+        <v>0.2145678152815336</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3390441115496401</v>
+        <v>0.3352966816805107</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2753713813301033</v>
+        <v>0.271220563003105</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.319203993388868</v>
+        <v>0.3143995189439082</v>
       </c>
     </row>
   </sheetData>
